--- a/research/traditional_assets/database/data/finland/finland_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_office_equipment_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hlse_maras" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0863</v>
+        <v>-0.00911</v>
+      </c>
+      <c r="E2">
+        <v>0.495</v>
       </c>
       <c r="G2">
-        <v>0.01494370522006141</v>
+        <v>0.0297196261682243</v>
       </c>
       <c r="H2">
-        <v>-0.008393039918116683</v>
+        <v>0.009906542056074767</v>
       </c>
       <c r="I2">
-        <v>-0.05926305015353121</v>
+        <v>0.03429906542056075</v>
       </c>
       <c r="J2">
-        <v>-0.05926305015353121</v>
+        <v>0.03429906542056075</v>
       </c>
       <c r="K2">
-        <v>-6.54</v>
+        <v>2.98</v>
       </c>
       <c r="L2">
-        <v>-0.0669396110542477</v>
+        <v>0.02785046728971963</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.96</v>
+        <v>7.58</v>
       </c>
       <c r="V2">
-        <v>0.5094017094017095</v>
+        <v>0.6423728813559322</v>
       </c>
       <c r="W2">
-        <v>-0.4219354838709677</v>
+        <v>0.2865384615384615</v>
       </c>
       <c r="X2">
-        <v>0.108713303224814</v>
+        <v>0.1612401938950221</v>
       </c>
       <c r="Y2">
-        <v>-0.5306487870957818</v>
+        <v>0.1252982676434394</v>
       </c>
       <c r="Z2">
-        <v>4.984693877551021</v>
+        <v>5.504115226337449</v>
       </c>
       <c r="AA2">
-        <v>-0.2954081632653062</v>
+        <v>0.1887860082304527</v>
       </c>
       <c r="AB2">
-        <v>0.05964902613058051</v>
+        <v>0.09293775102331493</v>
       </c>
       <c r="AC2">
-        <v>-0.3550571893958867</v>
+        <v>0.09584825720713776</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="AG2">
-        <v>9.039999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="AH2">
-        <v>0.5617977528089888</v>
+        <v>0.6026936026936026</v>
       </c>
       <c r="AI2">
-        <v>0.5905511811023623</v>
+        <v>0.5849673202614379</v>
       </c>
       <c r="AJ2">
-        <v>0.4358727097396335</v>
+        <v>0.4665461121157324</v>
       </c>
       <c r="AK2">
-        <v>0.4650205761316872</v>
+        <v>0.4483058210251955</v>
       </c>
       <c r="AL2">
-        <v>0.504</v>
+        <v>0.533</v>
       </c>
       <c r="AM2">
-        <v>0.483</v>
+        <v>0.513</v>
       </c>
       <c r="AN2">
-        <v>-7.5</v>
+        <v>2.924836601307189</v>
       </c>
       <c r="AO2">
-        <v>-11.48809523809524</v>
+        <v>6.885553470919324</v>
       </c>
       <c r="AP2">
-        <v>-4.52</v>
+        <v>1.686274509803921</v>
       </c>
       <c r="AQ2">
-        <v>-11.98757763975155</v>
+        <v>7.153996101364522</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0863</v>
+        <v>-0.00911</v>
+      </c>
+      <c r="E3">
+        <v>0.495</v>
       </c>
       <c r="G3">
-        <v>0.01494370522006141</v>
+        <v>0.0297196261682243</v>
       </c>
       <c r="H3">
-        <v>-0.008393039918116683</v>
+        <v>0.009906542056074767</v>
       </c>
       <c r="I3">
-        <v>-0.05926305015353121</v>
+        <v>0.03429906542056075</v>
       </c>
       <c r="J3">
-        <v>-0.05926305015353121</v>
+        <v>0.03429906542056075</v>
       </c>
       <c r="K3">
-        <v>-6.54</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
-        <v>-0.0669396110542477</v>
+        <v>0.02785046728971963</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.96</v>
+        <v>7.58</v>
       </c>
       <c r="V3">
-        <v>0.5094017094017095</v>
+        <v>0.6423728813559322</v>
       </c>
       <c r="W3">
-        <v>-0.4219354838709677</v>
+        <v>0.2865384615384615</v>
       </c>
       <c r="X3">
-        <v>0.108713303224814</v>
+        <v>0.1612401938950221</v>
       </c>
       <c r="Y3">
-        <v>-0.5306487870957818</v>
+        <v>0.1252982676434394</v>
       </c>
       <c r="Z3">
-        <v>4.984693877551021</v>
+        <v>5.504115226337449</v>
       </c>
       <c r="AA3">
-        <v>-0.2954081632653062</v>
+        <v>0.1887860082304527</v>
       </c>
       <c r="AB3">
-        <v>0.05964902613058051</v>
+        <v>0.09293775102331493</v>
       </c>
       <c r="AC3">
-        <v>-0.3550571893958867</v>
+        <v>0.09584825720713776</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="AG3">
-        <v>9.039999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="AH3">
-        <v>0.5617977528089888</v>
+        <v>0.6026936026936026</v>
       </c>
       <c r="AI3">
-        <v>0.5905511811023623</v>
+        <v>0.5849673202614379</v>
       </c>
       <c r="AJ3">
-        <v>0.4358727097396335</v>
+        <v>0.4665461121157324</v>
       </c>
       <c r="AK3">
-        <v>0.4650205761316872</v>
+        <v>0.4483058210251955</v>
       </c>
       <c r="AL3">
-        <v>0.504</v>
+        <v>0.533</v>
       </c>
       <c r="AM3">
-        <v>0.483</v>
+        <v>0.513</v>
       </c>
       <c r="AN3">
-        <v>-7.5</v>
+        <v>2.924836601307189</v>
       </c>
       <c r="AO3">
-        <v>-11.48809523809524</v>
+        <v>6.885553470919324</v>
       </c>
       <c r="AP3">
-        <v>-4.52</v>
+        <v>1.686274509803921</v>
       </c>
       <c r="AQ3">
-        <v>-11.98757763975155</v>
+        <v>7.153996101364522</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Martela Oyj (HLSE:MARAS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLSE:MARAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Office Equipment &amp; Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.6026936026936029</v>
+      </c>
+      <c r="F2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G2">
+        <v>11.8</v>
+      </c>
+      <c r="H2">
+        <v>27.5392063468047</v>
+      </c>
+      <c r="I2">
+        <v>22.12</v>
+      </c>
+      <c r="J2">
+        <v>22.0382063468047</v>
+      </c>
+      <c r="K2">
+        <v>17.9</v>
+      </c>
+      <c r="L2">
+        <v>2.079</v>
+      </c>
+      <c r="M2">
+        <v>0.0929377510233149</v>
+      </c>
+      <c r="N2">
+        <v>0.0937033249590277</v>
+      </c>
+      <c r="O2">
+        <v>0.0479115596330275</v>
+      </c>
+      <c r="P2">
+        <v>0.044</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.161240193895022</v>
+      </c>
+      <c r="T2">
+        <v>0.09744443543981469</v>
+      </c>
+      <c r="U2">
+        <v>1.8540425637213</v>
+      </c>
+      <c r="V2">
+        <v>0.88801949729061</v>
+      </c>
+      <c r="W2">
+        <v>4.897459442913991</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>11.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0660395809086869</v>
+      </c>
+      <c r="AC2">
+        <v>0.0598894495412844</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.12</v>
+      </c>
+      <c r="AH2">
+        <v>5.56</v>
+      </c>
+      <c r="AI2">
+        <v>0.862000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>17.9</v>
+      </c>
+      <c r="AK2">
+        <v>17.9</v>
+      </c>
+      <c r="AL2">
+        <v>0.533</v>
+      </c>
+      <c r="AM2">
+        <v>17.9</v>
+      </c>
+      <c r="AN2">
+        <v>7.58</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09411371699698548</v>
+      </c>
+      <c r="C2">
+        <v>29.57460875395259</v>
+      </c>
+      <c r="D2">
+        <v>21.99460875395259</v>
+      </c>
+      <c r="E2">
+        <v>-17.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>7.58</v>
+      </c>
+      <c r="H2">
+        <v>11.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.12</v>
+      </c>
+      <c r="K2">
+        <v>5.56</v>
+      </c>
+      <c r="L2">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="O2">
+        <v>0.1120000000000001</v>
+      </c>
+      <c r="P2">
+        <v>0.4480000000000004</v>
+      </c>
+      <c r="Q2">
+        <v>6.008</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09411371699698548</v>
+      </c>
+      <c r="T2">
+        <v>0.8375843128603115</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09398068956299151</v>
+      </c>
+      <c r="C3">
+        <v>29.2917218850637</v>
+      </c>
+      <c r="D3">
+        <v>22.0087218850637</v>
+      </c>
+      <c r="E3">
+        <v>-17.603</v>
+      </c>
+      <c r="F3">
+        <v>0.297</v>
+      </c>
+      <c r="G3">
+        <v>7.58</v>
+      </c>
+      <c r="H3">
+        <v>11.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.12</v>
+      </c>
+      <c r="K3">
+        <v>5.56</v>
+      </c>
+      <c r="L3">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M3">
+        <v>0.0135729</v>
+      </c>
+      <c r="N3">
+        <v>0.5464271000000005</v>
+      </c>
+      <c r="O3">
+        <v>0.1092854200000001</v>
+      </c>
+      <c r="P3">
+        <v>0.4371416800000004</v>
+      </c>
+      <c r="Q3">
+        <v>5.99714168</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09456069652827426</v>
+      </c>
+      <c r="T3">
+        <v>0.8443526709440313</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>41.25868458472401</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09384766212899752</v>
+      </c>
+      <c r="C4">
+        <v>29.00885313955775</v>
+      </c>
+      <c r="D4">
+        <v>22.02285313955775</v>
+      </c>
+      <c r="E4">
+        <v>-17.306</v>
+      </c>
+      <c r="F4">
+        <v>0.594</v>
+      </c>
+      <c r="G4">
+        <v>7.58</v>
+      </c>
+      <c r="H4">
+        <v>11.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.12</v>
+      </c>
+      <c r="K4">
+        <v>5.56</v>
+      </c>
+      <c r="L4">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M4">
+        <v>0.0271458</v>
+      </c>
+      <c r="N4">
+        <v>0.5328542000000005</v>
+      </c>
+      <c r="O4">
+        <v>0.1065708400000001</v>
+      </c>
+      <c r="P4">
+        <v>0.4262833600000004</v>
+      </c>
+      <c r="Q4">
+        <v>5.98628336</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.0950167980908138</v>
+      </c>
+      <c r="T4">
+        <v>0.8512591587845615</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>20.629342292362</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09371463469500355</v>
+      </c>
+      <c r="C5">
+        <v>28.72600255236691</v>
+      </c>
+      <c r="D5">
+        <v>22.03700255236691</v>
+      </c>
+      <c r="E5">
+        <v>-17.009</v>
+      </c>
+      <c r="F5">
+        <v>0.8909999999999999</v>
+      </c>
+      <c r="G5">
+        <v>7.58</v>
+      </c>
+      <c r="H5">
+        <v>11.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.12</v>
+      </c>
+      <c r="K5">
+        <v>5.56</v>
+      </c>
+      <c r="L5">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M5">
+        <v>0.0407187</v>
+      </c>
+      <c r="N5">
+        <v>0.5192813000000005</v>
+      </c>
+      <c r="O5">
+        <v>0.1038562600000001</v>
+      </c>
+      <c r="P5">
+        <v>0.4154250400000004</v>
+      </c>
+      <c r="Q5">
+        <v>5.97542504</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09548230380928201</v>
+      </c>
+      <c r="T5">
+        <v>0.8583080484362366</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>13.75289486157467</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.0937544072610096</v>
+      </c>
+      <c r="C6">
+        <v>28.4247702534055</v>
+      </c>
+      <c r="D6">
+        <v>22.0327702534055</v>
+      </c>
+      <c r="E6">
+        <v>-16.712</v>
+      </c>
+      <c r="F6">
+        <v>1.188</v>
+      </c>
+      <c r="G6">
+        <v>7.58</v>
+      </c>
+      <c r="H6">
+        <v>11.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.12</v>
+      </c>
+      <c r="K6">
+        <v>5.56</v>
+      </c>
+      <c r="L6">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M6">
+        <v>0.0607068</v>
+      </c>
+      <c r="N6">
+        <v>0.4992932000000005</v>
+      </c>
+      <c r="O6">
+        <v>0.09985864000000008</v>
+      </c>
+      <c r="P6">
+        <v>0.3994345600000004</v>
+      </c>
+      <c r="Q6">
+        <v>5.95943456</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09595750756355166</v>
+      </c>
+      <c r="T6">
+        <v>0.8655037899556554</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.04088</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>9.224666758913342</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0937405798270156</v>
+      </c>
+      <c r="C7">
+        <v>28.12924148114011</v>
+      </c>
+      <c r="D7">
+        <v>22.0342414811401</v>
+      </c>
+      <c r="E7">
+        <v>-16.415</v>
+      </c>
+      <c r="F7">
+        <v>1.485</v>
+      </c>
+      <c r="G7">
+        <v>7.58</v>
+      </c>
+      <c r="H7">
+        <v>11.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.12</v>
+      </c>
+      <c r="K7">
+        <v>5.56</v>
+      </c>
+      <c r="L7">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M7">
+        <v>0.07870500000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.4812950000000005</v>
+      </c>
+      <c r="O7">
+        <v>0.09625900000000007</v>
+      </c>
+      <c r="P7">
+        <v>0.3850360000000004</v>
+      </c>
+      <c r="Q7">
+        <v>5.945036</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09644271560738485</v>
+      </c>
+      <c r="T7">
+        <v>0.8728510207702194</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>7.115176926497687</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09376195239302164</v>
+      </c>
+      <c r="C8">
+        <v>27.82996754034276</v>
+      </c>
+      <c r="D8">
+        <v>22.03196754034276</v>
+      </c>
+      <c r="E8">
+        <v>-16.118</v>
+      </c>
+      <c r="F8">
+        <v>1.782</v>
+      </c>
+      <c r="G8">
+        <v>7.58</v>
+      </c>
+      <c r="H8">
+        <v>11.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.12</v>
+      </c>
+      <c r="K8">
+        <v>5.56</v>
+      </c>
+      <c r="L8">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M8">
+        <v>0.09800999999999999</v>
+      </c>
+      <c r="N8">
+        <v>0.4619900000000005</v>
+      </c>
+      <c r="O8">
+        <v>0.09239800000000008</v>
+      </c>
+      <c r="P8">
+        <v>0.3695920000000004</v>
+      </c>
+      <c r="Q8">
+        <v>5.929592</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09693824722661877</v>
+      </c>
+      <c r="T8">
+        <v>0.8803545756446679</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.044</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.713702683399659</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09370332495902767</v>
+      </c>
+      <c r="C9">
+        <v>27.5392063468047</v>
+      </c>
+      <c r="D9">
+        <v>22.03820634680471</v>
+      </c>
+      <c r="E9">
+        <v>-15.821</v>
+      </c>
+      <c r="F9">
+        <v>2.079</v>
+      </c>
+      <c r="G9">
+        <v>7.58</v>
+      </c>
+      <c r="H9">
+        <v>11.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.12</v>
+      </c>
+      <c r="K9">
+        <v>5.56</v>
+      </c>
+      <c r="L9">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M9">
+        <v>0.114345</v>
+      </c>
+      <c r="N9">
+        <v>0.4456550000000005</v>
+      </c>
+      <c r="O9">
+        <v>0.08913100000000007</v>
+      </c>
+      <c r="P9">
+        <v>0.3565240000000004</v>
+      </c>
+      <c r="Q9">
+        <v>5.916524</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09744443543981471</v>
+      </c>
+      <c r="T9">
+        <v>0.8880194972906099</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.044</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>4.897459442913991</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.0938878975250337</v>
+      </c>
+      <c r="C10">
+        <v>27.22257709509871</v>
+      </c>
+      <c r="D10">
+        <v>22.01857709509871</v>
+      </c>
+      <c r="E10">
+        <v>-15.524</v>
+      </c>
+      <c r="F10">
+        <v>2.376</v>
+      </c>
+      <c r="G10">
+        <v>7.58</v>
+      </c>
+      <c r="H10">
+        <v>11.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.12</v>
+      </c>
+      <c r="K10">
+        <v>5.56</v>
+      </c>
+      <c r="L10">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M10">
+        <v>0.1397088</v>
+      </c>
+      <c r="N10">
+        <v>0.4202912000000005</v>
+      </c>
+      <c r="O10">
+        <v>0.08405824000000009</v>
+      </c>
+      <c r="P10">
+        <v>0.3362329600000005</v>
+      </c>
+      <c r="Q10">
+        <v>5.89623296</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09796162774460185</v>
+      </c>
+      <c r="T10">
+        <v>0.8958510476679854</v>
+      </c>
+      <c r="U10">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.008337341670678</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09620687009103973</v>
+      </c>
+      <c r="C11">
+        <v>26.68190143145764</v>
+      </c>
+      <c r="D11">
+        <v>21.77490143145764</v>
+      </c>
+      <c r="E11">
+        <v>-15.227</v>
+      </c>
+      <c r="F11">
+        <v>2.673</v>
+      </c>
+      <c r="G11">
+        <v>7.58</v>
+      </c>
+      <c r="H11">
+        <v>11.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.12</v>
+      </c>
+      <c r="K11">
+        <v>5.56</v>
+      </c>
+      <c r="L11">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M11">
+        <v>0.2443122</v>
+      </c>
+      <c r="N11">
+        <v>0.3156878000000005</v>
+      </c>
+      <c r="O11">
+        <v>0.06313756000000008</v>
+      </c>
+      <c r="P11">
+        <v>0.2525502400000004</v>
+      </c>
+      <c r="Q11">
+        <v>5.81255024</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09849018691323047</v>
+      </c>
+      <c r="T11">
+        <v>0.9038547200316768</v>
+      </c>
+      <c r="U11">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.07312</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>2.292149143595778</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09643944265704578</v>
+      </c>
+      <c r="C12">
+        <v>26.36076015549794</v>
+      </c>
+      <c r="D12">
+        <v>21.75076015549794</v>
+      </c>
+      <c r="E12">
+        <v>-14.93</v>
+      </c>
+      <c r="F12">
+        <v>2.97</v>
+      </c>
+      <c r="G12">
+        <v>7.58</v>
+      </c>
+      <c r="H12">
+        <v>11.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.12</v>
+      </c>
+      <c r="K12">
+        <v>5.56</v>
+      </c>
+      <c r="L12">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M12">
+        <v>0.271458</v>
+      </c>
+      <c r="N12">
+        <v>0.2885420000000005</v>
+      </c>
+      <c r="O12">
+        <v>0.05770840000000008</v>
+      </c>
+      <c r="P12">
+        <v>0.2308336000000004</v>
+      </c>
+      <c r="Q12">
+        <v>5.7908336</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09903049184116197</v>
+      </c>
+      <c r="T12">
+        <v>0.9120362517812283</v>
+      </c>
+      <c r="U12">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.07312</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.0629342292362</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09852881522305179</v>
+      </c>
+      <c r="C13">
+        <v>25.84925799468867</v>
+      </c>
+      <c r="D13">
+        <v>21.53625799468868</v>
+      </c>
+      <c r="E13">
+        <v>-14.633</v>
+      </c>
+      <c r="F13">
+        <v>3.267</v>
+      </c>
+      <c r="G13">
+        <v>7.58</v>
+      </c>
+      <c r="H13">
+        <v>11.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.12</v>
+      </c>
+      <c r="K13">
+        <v>5.56</v>
+      </c>
+      <c r="L13">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M13">
+        <v>0.3675375</v>
+      </c>
+      <c r="N13">
+        <v>0.1924625000000005</v>
+      </c>
+      <c r="O13">
+        <v>0.03849250000000009</v>
+      </c>
+      <c r="P13">
+        <v>0.1539700000000004</v>
+      </c>
+      <c r="Q13">
+        <v>5.71397</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09958293845286717</v>
+      </c>
+      <c r="T13">
+        <v>0.9204016381768366</v>
+      </c>
+      <c r="U13">
+        <v>0.1125</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>1.523654048906575</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1103670396995864</v>
+      </c>
+      <c r="C14">
+        <v>24.41257228285351</v>
+      </c>
+      <c r="D14">
+        <v>20.39657228285351</v>
+      </c>
+      <c r="E14">
+        <v>-14.336</v>
+      </c>
+      <c r="F14">
+        <v>3.564</v>
+      </c>
+      <c r="G14">
+        <v>7.58</v>
+      </c>
+      <c r="H14">
+        <v>11.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.12</v>
+      </c>
+      <c r="K14">
+        <v>5.56</v>
+      </c>
+      <c r="L14">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M14">
+        <v>0.7619831999999999</v>
+      </c>
+      <c r="N14">
+        <v>-0.2019831999999994</v>
+      </c>
+      <c r="O14">
+        <v>-0.04039663999999987</v>
+      </c>
+      <c r="P14">
+        <v>-0.1615865599999995</v>
+      </c>
+      <c r="Q14">
+        <v>5.398413440000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1005478221257161</v>
+      </c>
+      <c r="T14">
+        <v>0.9350123255793369</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.146984867907849</v>
+      </c>
+      <c r="W14">
+        <v>0.1823746352413019</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.7349243395392453</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1121170396995864</v>
+      </c>
+      <c r="C15">
+        <v>23.95725099499444</v>
+      </c>
+      <c r="D15">
+        <v>20.23825099499444</v>
+      </c>
+      <c r="E15">
+        <v>-14.039</v>
+      </c>
+      <c r="F15">
+        <v>3.861</v>
+      </c>
+      <c r="G15">
+        <v>7.58</v>
+      </c>
+      <c r="H15">
+        <v>11.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.12</v>
+      </c>
+      <c r="K15">
+        <v>5.56</v>
+      </c>
+      <c r="L15">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M15">
+        <v>0.8254818</v>
+      </c>
+      <c r="N15">
+        <v>-0.2654817999999995</v>
+      </c>
+      <c r="O15">
+        <v>-0.0530963599999999</v>
+      </c>
+      <c r="P15">
+        <v>-0.2123854399999996</v>
+      </c>
+      <c r="Q15">
+        <v>5.34761456</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1012575672076209</v>
+      </c>
+      <c r="T15">
+        <v>0.9457595936894443</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1356783396072452</v>
+      </c>
+      <c r="W15">
+        <v>0.184791970991971</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.6783916980362261</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1138670396995864</v>
+      </c>
+      <c r="C16">
+        <v>23.50436860375171</v>
+      </c>
+      <c r="D16">
+        <v>20.08236860375171</v>
+      </c>
+      <c r="E16">
+        <v>-13.742</v>
+      </c>
+      <c r="F16">
+        <v>4.158</v>
+      </c>
+      <c r="G16">
+        <v>7.58</v>
+      </c>
+      <c r="H16">
+        <v>11.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.12</v>
+      </c>
+      <c r="K16">
+        <v>5.56</v>
+      </c>
+      <c r="L16">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M16">
+        <v>0.8889804</v>
+      </c>
+      <c r="N16">
+        <v>-0.3289803999999995</v>
+      </c>
+      <c r="O16">
+        <v>-0.06579607999999988</v>
+      </c>
+      <c r="P16">
+        <v>-0.2631843199999996</v>
+      </c>
+      <c r="Q16">
+        <v>5.29681568</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1019838179891049</v>
+      </c>
+      <c r="T16">
+        <v>0.9567567982672283</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1259870296352991</v>
+      </c>
+      <c r="W16">
+        <v>0.186863973063973</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6299351481764958</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1156170396995864</v>
+      </c>
+      <c r="C17">
+        <v>23.05386918406648</v>
+      </c>
+      <c r="D17">
+        <v>19.92886918406648</v>
+      </c>
+      <c r="E17">
+        <v>-13.445</v>
+      </c>
+      <c r="F17">
+        <v>4.455</v>
+      </c>
+      <c r="G17">
+        <v>7.58</v>
+      </c>
+      <c r="H17">
+        <v>11.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.12</v>
+      </c>
+      <c r="K17">
+        <v>5.56</v>
+      </c>
+      <c r="L17">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M17">
+        <v>0.952479</v>
+      </c>
+      <c r="N17">
+        <v>-0.3924789999999995</v>
+      </c>
+      <c r="O17">
+        <v>-0.07849579999999988</v>
+      </c>
+      <c r="P17">
+        <v>-0.3139831999999996</v>
+      </c>
+      <c r="Q17">
+        <v>5.2460168</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1027271570242708</v>
+      </c>
+      <c r="T17">
+        <v>0.9680127605997841</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1175878943262792</v>
+      </c>
+      <c r="W17">
+        <v>0.1886597081930415</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5879394716313961</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1173670396995864</v>
+      </c>
+      <c r="C18">
+        <v>22.60569850776071</v>
+      </c>
+      <c r="D18">
+        <v>19.77769850776071</v>
+      </c>
+      <c r="E18">
+        <v>-13.148</v>
+      </c>
+      <c r="F18">
+        <v>4.752</v>
+      </c>
+      <c r="G18">
+        <v>7.58</v>
+      </c>
+      <c r="H18">
+        <v>11.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.12</v>
+      </c>
+      <c r="K18">
+        <v>5.56</v>
+      </c>
+      <c r="L18">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M18">
+        <v>1.0159776</v>
+      </c>
+      <c r="N18">
+        <v>-0.4559775999999993</v>
+      </c>
+      <c r="O18">
+        <v>-0.09119551999999985</v>
+      </c>
+      <c r="P18">
+        <v>-0.3647820799999995</v>
+      </c>
+      <c r="Q18">
+        <v>5.19521792</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1034881946078931</v>
+      </c>
+      <c r="T18">
+        <v>0.9795367220354958</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1102386509308868</v>
+      </c>
+      <c r="W18">
+        <v>0.1902309764309764</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5511932546544339</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1191170396995864</v>
+      </c>
+      <c r="C19">
+        <v>22.15980397966318</v>
+      </c>
+      <c r="D19">
+        <v>19.62880397966318</v>
+      </c>
+      <c r="E19">
+        <v>-12.851</v>
+      </c>
+      <c r="F19">
+        <v>5.049</v>
+      </c>
+      <c r="G19">
+        <v>7.58</v>
+      </c>
+      <c r="H19">
+        <v>11.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.12</v>
+      </c>
+      <c r="K19">
+        <v>5.56</v>
+      </c>
+      <c r="L19">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M19">
+        <v>1.0794762</v>
+      </c>
+      <c r="N19">
+        <v>-0.5194761999999995</v>
+      </c>
+      <c r="O19">
+        <v>-0.1038952399999999</v>
+      </c>
+      <c r="P19">
+        <v>-0.4155809599999996</v>
+      </c>
+      <c r="Q19">
+        <v>5.14441904</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1042675704465424</v>
+      </c>
+      <c r="T19">
+        <v>0.9913383692889354</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1037540244055405</v>
+      </c>
+      <c r="W19">
+        <v>0.1916173895820954</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5187701220277023</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1254691788878564</v>
+      </c>
+      <c r="C20">
+        <v>21.3406840572017</v>
+      </c>
+      <c r="D20">
+        <v>19.10668405720169</v>
+      </c>
+      <c r="E20">
+        <v>-12.554</v>
+      </c>
+      <c r="F20">
+        <v>5.346</v>
+      </c>
+      <c r="G20">
+        <v>7.58</v>
+      </c>
+      <c r="H20">
+        <v>11.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.12</v>
+      </c>
+      <c r="K20">
+        <v>5.56</v>
+      </c>
+      <c r="L20">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M20">
+        <v>1.2766248</v>
+      </c>
+      <c r="N20">
+        <v>-0.7166247999999995</v>
+      </c>
+      <c r="O20">
+        <v>-0.1433249599999999</v>
+      </c>
+      <c r="P20">
+        <v>-0.5732998399999997</v>
+      </c>
+      <c r="Q20">
+        <v>4.98670016</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1051905154376832</v>
+      </c>
+      <c r="T20">
+        <v>1.005314002968636</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.08773133656811309</v>
+      </c>
+      <c r="W20">
+        <v>0.2178497568275346</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.4386566828405656</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1274691788878564</v>
+      </c>
+      <c r="C21">
+        <v>20.88499402227089</v>
+      </c>
+      <c r="D21">
+        <v>18.94799402227089</v>
+      </c>
+      <c r="E21">
+        <v>-12.257</v>
+      </c>
+      <c r="F21">
+        <v>5.643</v>
+      </c>
+      <c r="G21">
+        <v>7.58</v>
+      </c>
+      <c r="H21">
+        <v>11.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.12</v>
+      </c>
+      <c r="K21">
+        <v>5.56</v>
+      </c>
+      <c r="L21">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M21">
+        <v>1.3475484</v>
+      </c>
+      <c r="N21">
+        <v>-0.7875483999999995</v>
+      </c>
+      <c r="O21">
+        <v>-0.1575096799999999</v>
+      </c>
+      <c r="P21">
+        <v>-0.6300387199999996</v>
+      </c>
+      <c r="Q21">
+        <v>4.92996128</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.106010151430741</v>
+      </c>
+      <c r="T21">
+        <v>1.017725286955904</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.08311389780137031</v>
+      </c>
+      <c r="W21">
+        <v>0.2189524012050328</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.4155694890068516</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1294691788878564</v>
+      </c>
+      <c r="C22">
+        <v>20.43191826589661</v>
+      </c>
+      <c r="D22">
+        <v>18.79191826589661</v>
+      </c>
+      <c r="E22">
+        <v>-11.96</v>
+      </c>
+      <c r="F22">
+        <v>5.94</v>
+      </c>
+      <c r="G22">
+        <v>7.58</v>
+      </c>
+      <c r="H22">
+        <v>11.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.12</v>
+      </c>
+      <c r="K22">
+        <v>5.56</v>
+      </c>
+      <c r="L22">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M22">
+        <v>1.418472</v>
+      </c>
+      <c r="N22">
+        <v>-0.8584719999999997</v>
+      </c>
+      <c r="O22">
+        <v>-0.1716943999999999</v>
+      </c>
+      <c r="P22">
+        <v>-0.6867775999999998</v>
+      </c>
+      <c r="Q22">
+        <v>4.8732224</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1068502783236253</v>
+      </c>
+      <c r="T22">
+        <v>1.030446853042852</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.07895820291130179</v>
+      </c>
+      <c r="W22">
+        <v>0.2199447811447811</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.394791014556509</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1314691788878564</v>
+      </c>
+      <c r="C23">
+        <v>19.98139271395626</v>
+      </c>
+      <c r="D23">
+        <v>18.63839271395626</v>
+      </c>
+      <c r="E23">
+        <v>-11.663</v>
+      </c>
+      <c r="F23">
+        <v>6.236999999999999</v>
+      </c>
+      <c r="G23">
+        <v>7.58</v>
+      </c>
+      <c r="H23">
+        <v>11.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.12</v>
+      </c>
+      <c r="K23">
+        <v>5.56</v>
+      </c>
+      <c r="L23">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M23">
+        <v>1.4893956</v>
+      </c>
+      <c r="N23">
+        <v>-0.9293955999999994</v>
+      </c>
+      <c r="O23">
+        <v>-0.1858791199999998</v>
+      </c>
+      <c r="P23">
+        <v>-0.7435164799999996</v>
+      </c>
+      <c r="Q23">
+        <v>4.81648352</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1077116742517724</v>
+      </c>
+      <c r="T23">
+        <v>1.043490484094028</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07519828848695409</v>
+      </c>
+      <c r="W23">
+        <v>0.2208426487093154</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3759914424347706</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1334691788878564</v>
+      </c>
+      <c r="C24">
+        <v>19.53335536924138</v>
+      </c>
+      <c r="D24">
+        <v>18.48735536924139</v>
+      </c>
+      <c r="E24">
+        <v>-11.366</v>
+      </c>
+      <c r="F24">
+        <v>6.534</v>
+      </c>
+      <c r="G24">
+        <v>7.58</v>
+      </c>
+      <c r="H24">
+        <v>11.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.12</v>
+      </c>
+      <c r="K24">
+        <v>5.56</v>
+      </c>
+      <c r="L24">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M24">
+        <v>1.5603192</v>
+      </c>
+      <c r="N24">
+        <v>-1.0003192</v>
+      </c>
+      <c r="O24">
+        <v>-0.2000638399999999</v>
+      </c>
+      <c r="P24">
+        <v>-0.8002553599999997</v>
+      </c>
+      <c r="Q24">
+        <v>4.75974464</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1085951572550003</v>
+      </c>
+      <c r="T24">
+        <v>1.056868567223438</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.0717801844648198</v>
+      </c>
+      <c r="W24">
+        <v>0.221658891949801</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3589009223240991</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1354691788878565</v>
+      </c>
+      <c r="C25">
+        <v>19.08774622798209</v>
+      </c>
+      <c r="D25">
+        <v>18.33874622798209</v>
+      </c>
+      <c r="E25">
+        <v>-11.069</v>
+      </c>
+      <c r="F25">
+        <v>6.831</v>
+      </c>
+      <c r="G25">
+        <v>7.58</v>
+      </c>
+      <c r="H25">
+        <v>11.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.12</v>
+      </c>
+      <c r="K25">
+        <v>5.56</v>
+      </c>
+      <c r="L25">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M25">
+        <v>1.6312428</v>
+      </c>
+      <c r="N25">
+        <v>-1.0712428</v>
+      </c>
+      <c r="O25">
+        <v>-0.2142485599999999</v>
+      </c>
+      <c r="P25">
+        <v>-0.8569942399999997</v>
+      </c>
+      <c r="Q25">
+        <v>4.70300576</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1095015878687016</v>
+      </c>
+      <c r="T25">
+        <v>1.070594133031535</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.06865930687939287</v>
+      </c>
+      <c r="W25">
+        <v>0.222404157517201</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3432965343969644</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1374691788878564</v>
+      </c>
+      <c r="C26">
+        <v>18.64450720036553</v>
+      </c>
+      <c r="D26">
+        <v>18.19250720036553</v>
+      </c>
+      <c r="E26">
+        <v>-10.772</v>
+      </c>
+      <c r="F26">
+        <v>7.127999999999999</v>
+      </c>
+      <c r="G26">
+        <v>7.58</v>
+      </c>
+      <c r="H26">
+        <v>11.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.12</v>
+      </c>
+      <c r="K26">
+        <v>5.56</v>
+      </c>
+      <c r="L26">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M26">
+        <v>1.7021664</v>
+      </c>
+      <c r="N26">
+        <v>-1.142166399999999</v>
+      </c>
+      <c r="O26">
+        <v>-0.2284332799999998</v>
+      </c>
+      <c r="P26">
+        <v>-0.9137331199999995</v>
+      </c>
+      <c r="Q26">
+        <v>4.64626688</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1104318719196055</v>
+      </c>
+      <c r="T26">
+        <v>1.084680897939845</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06579850242608483</v>
+      </c>
+      <c r="W26">
+        <v>0.223087317620651</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3289925121304242</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1394691788878564</v>
+      </c>
+      <c r="C27">
+        <v>18.20358203482703</v>
+      </c>
+      <c r="D27">
+        <v>18.04858203482702</v>
+      </c>
+      <c r="E27">
+        <v>-10.475</v>
+      </c>
+      <c r="F27">
+        <v>7.425</v>
+      </c>
+      <c r="G27">
+        <v>7.58</v>
+      </c>
+      <c r="H27">
+        <v>11.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.12</v>
+      </c>
+      <c r="K27">
+        <v>5.56</v>
+      </c>
+      <c r="L27">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M27">
+        <v>1.77309</v>
+      </c>
+      <c r="N27">
+        <v>-1.21309</v>
+      </c>
+      <c r="O27">
+        <v>-0.2426179999999999</v>
+      </c>
+      <c r="P27">
+        <v>-0.9704719999999997</v>
+      </c>
+      <c r="Q27">
+        <v>4.589528</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1113869635452003</v>
+      </c>
+      <c r="T27">
+        <v>1.099143309912376</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06316656232904143</v>
+      </c>
+      <c r="W27">
+        <v>0.2237158249158249</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3158328116452073</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1414691788878564</v>
+      </c>
+      <c r="C28">
+        <v>17.76491624590682</v>
+      </c>
+      <c r="D28">
+        <v>17.90691624590682</v>
+      </c>
+      <c r="E28">
+        <v>-10.178</v>
+      </c>
+      <c r="F28">
+        <v>7.722</v>
+      </c>
+      <c r="G28">
+        <v>7.58</v>
+      </c>
+      <c r="H28">
+        <v>11.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.12</v>
+      </c>
+      <c r="K28">
+        <v>5.56</v>
+      </c>
+      <c r="L28">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M28">
+        <v>1.8440136</v>
+      </c>
+      <c r="N28">
+        <v>-1.2840136</v>
+      </c>
+      <c r="O28">
+        <v>-0.2568027199999999</v>
+      </c>
+      <c r="P28">
+        <v>-1.02721088</v>
+      </c>
+      <c r="Q28">
+        <v>4.532789119999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1123678684579733</v>
+      </c>
+      <c r="T28">
+        <v>1.113996597884165</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06073707916253983</v>
+      </c>
+      <c r="W28">
+        <v>0.2242959854959855</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3036853958126993</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1434691788878565</v>
+      </c>
+      <c r="C29">
+        <v>17.32845704547786</v>
+      </c>
+      <c r="D29">
+        <v>17.76745704547786</v>
+      </c>
+      <c r="E29">
+        <v>-9.880999999999998</v>
+      </c>
+      <c r="F29">
+        <v>8.019</v>
+      </c>
+      <c r="G29">
+        <v>7.58</v>
+      </c>
+      <c r="H29">
+        <v>11.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.12</v>
+      </c>
+      <c r="K29">
+        <v>5.56</v>
+      </c>
+      <c r="L29">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M29">
+        <v>1.9149372</v>
+      </c>
+      <c r="N29">
+        <v>-1.3549372</v>
+      </c>
+      <c r="O29">
+        <v>-0.2709874399999999</v>
+      </c>
+      <c r="P29">
+        <v>-1.08394976</v>
+      </c>
+      <c r="Q29">
+        <v>4.476050239999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1133756474779455</v>
+      </c>
+      <c r="T29">
+        <v>1.129256825252441</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.0584875577120754</v>
+      </c>
+      <c r="W29">
+        <v>0.2248331712183564</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2924377885603771</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1454691788878565</v>
+      </c>
+      <c r="C30">
+        <v>16.89415327716235</v>
+      </c>
+      <c r="D30">
+        <v>17.63015327716236</v>
+      </c>
+      <c r="E30">
+        <v>-9.583999999999998</v>
+      </c>
+      <c r="F30">
+        <v>8.316000000000001</v>
+      </c>
+      <c r="G30">
+        <v>7.58</v>
+      </c>
+      <c r="H30">
+        <v>11.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.12</v>
+      </c>
+      <c r="K30">
+        <v>5.56</v>
+      </c>
+      <c r="L30">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M30">
+        <v>1.9858608</v>
+      </c>
+      <c r="N30">
+        <v>-1.4258608</v>
+      </c>
+      <c r="O30">
+        <v>-0.2851721599999999</v>
+      </c>
+      <c r="P30">
+        <v>-1.14068864</v>
+      </c>
+      <c r="Q30">
+        <v>4.41931136</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1144114203595836</v>
+      </c>
+      <c r="T30">
+        <v>1.144940947825392</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05639871636521556</v>
+      </c>
+      <c r="W30">
+        <v>0.2253319865319866</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2819935818260778</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1474691788878564</v>
+      </c>
+      <c r="C31">
+        <v>16.46195535376595</v>
+      </c>
+      <c r="D31">
+        <v>17.49495535376595</v>
+      </c>
+      <c r="E31">
+        <v>-9.286999999999999</v>
+      </c>
+      <c r="F31">
+        <v>8.613</v>
+      </c>
+      <c r="G31">
+        <v>7.58</v>
+      </c>
+      <c r="H31">
+        <v>11.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.12</v>
+      </c>
+      <c r="K31">
+        <v>5.56</v>
+      </c>
+      <c r="L31">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M31">
+        <v>2.0567844</v>
+      </c>
+      <c r="N31">
+        <v>-1.4967844</v>
+      </c>
+      <c r="O31">
+        <v>-0.2993568799999999</v>
+      </c>
+      <c r="P31">
+        <v>-1.19742752</v>
+      </c>
+      <c r="Q31">
+        <v>4.36257248</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.115476369942113</v>
+      </c>
+      <c r="T31">
+        <v>1.161066876668003</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05445393304227709</v>
+      </c>
+      <c r="W31">
+        <v>0.2257964007895042</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2722696652113855</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1494691788878564</v>
+      </c>
+      <c r="C32">
+        <v>16.03181519756867</v>
+      </c>
+      <c r="D32">
+        <v>17.36181519756867</v>
+      </c>
+      <c r="E32">
+        <v>-8.989999999999998</v>
+      </c>
+      <c r="F32">
+        <v>8.91</v>
+      </c>
+      <c r="G32">
+        <v>7.58</v>
+      </c>
+      <c r="H32">
+        <v>11.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.12</v>
+      </c>
+      <c r="K32">
+        <v>5.56</v>
+      </c>
+      <c r="L32">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M32">
+        <v>2.127708</v>
+      </c>
+      <c r="N32">
+        <v>-1.567708</v>
+      </c>
+      <c r="O32">
+        <v>-0.3135415999999999</v>
+      </c>
+      <c r="P32">
+        <v>-1.2541664</v>
+      </c>
+      <c r="Q32">
+        <v>4.3058336</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1165717466555717</v>
+      </c>
+      <c r="T32">
+        <v>1.177653546334688</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05263880194086786</v>
+      </c>
+      <c r="W32">
+        <v>0.2262298540965208</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2631940097043394</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1514691788878564</v>
+      </c>
+      <c r="C33">
+        <v>15.60368618332171</v>
+      </c>
+      <c r="D33">
+        <v>17.23068618332171</v>
+      </c>
+      <c r="E33">
+        <v>-8.693</v>
+      </c>
+      <c r="F33">
+        <v>9.206999999999999</v>
+      </c>
+      <c r="G33">
+        <v>7.58</v>
+      </c>
+      <c r="H33">
+        <v>11.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.12</v>
+      </c>
+      <c r="K33">
+        <v>5.56</v>
+      </c>
+      <c r="L33">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M33">
+        <v>2.1986316</v>
+      </c>
+      <c r="N33">
+        <v>-1.638631599999999</v>
+      </c>
+      <c r="O33">
+        <v>-0.3277263199999997</v>
+      </c>
+      <c r="P33">
+        <v>-1.310905279999999</v>
+      </c>
+      <c r="Q33">
+        <v>4.24909472</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.117698873418696</v>
+      </c>
+      <c r="T33">
+        <v>1.194720989035191</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.05094077607180762</v>
+      </c>
+      <c r="W33">
+        <v>0.2266353426740524</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2547038803590381</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1534691788878564</v>
+      </c>
+      <c r="C34">
+        <v>15.17752308380805</v>
+      </c>
+      <c r="D34">
+        <v>17.10152308380805</v>
+      </c>
+      <c r="E34">
+        <v>-8.395999999999999</v>
+      </c>
+      <c r="F34">
+        <v>9.504</v>
+      </c>
+      <c r="G34">
+        <v>7.58</v>
+      </c>
+      <c r="H34">
+        <v>11.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.12</v>
+      </c>
+      <c r="K34">
+        <v>5.56</v>
+      </c>
+      <c r="L34">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M34">
+        <v>2.2695552</v>
+      </c>
+      <c r="N34">
+        <v>-1.7095552</v>
+      </c>
+      <c r="O34">
+        <v>-0.3419110399999998</v>
+      </c>
+      <c r="P34">
+        <v>-1.36764416</v>
+      </c>
+      <c r="Q34">
+        <v>4.192355839999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1188591509689709</v>
+      </c>
+      <c r="T34">
+        <v>1.212290415344532</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.04934887681956362</v>
+      </c>
+      <c r="W34">
+        <v>0.2270154882154882</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2467443840978182</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1554691788878564</v>
+      </c>
+      <c r="C35">
+        <v>14.75328201783329</v>
+      </c>
+      <c r="D35">
+        <v>16.97428201783329</v>
+      </c>
+      <c r="E35">
+        <v>-8.098999999999998</v>
+      </c>
+      <c r="F35">
+        <v>9.801</v>
+      </c>
+      <c r="G35">
+        <v>7.58</v>
+      </c>
+      <c r="H35">
+        <v>11.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.12</v>
+      </c>
+      <c r="K35">
+        <v>5.56</v>
+      </c>
+      <c r="L35">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M35">
+        <v>2.3404788</v>
+      </c>
+      <c r="N35">
+        <v>-1.7804788</v>
+      </c>
+      <c r="O35">
+        <v>-0.3560957599999998</v>
+      </c>
+      <c r="P35">
+        <v>-1.42438304</v>
+      </c>
+      <c r="Q35">
+        <v>4.13561696</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1200540636700003</v>
+      </c>
+      <c r="T35">
+        <v>1.230384302140719</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.04785345630987987</v>
+      </c>
+      <c r="W35">
+        <v>0.2273725946332007</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2392672815493994</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1574691788878564</v>
+      </c>
+      <c r="C36">
+        <v>14.33092040052121</v>
+      </c>
+      <c r="D36">
+        <v>16.84892040052121</v>
+      </c>
+      <c r="E36">
+        <v>-7.801999999999998</v>
+      </c>
+      <c r="F36">
+        <v>10.098</v>
+      </c>
+      <c r="G36">
+        <v>7.58</v>
+      </c>
+      <c r="H36">
+        <v>11.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.12</v>
+      </c>
+      <c r="K36">
+        <v>5.56</v>
+      </c>
+      <c r="L36">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M36">
+        <v>2.411402400000001</v>
+      </c>
+      <c r="N36">
+        <v>-1.8514024</v>
+      </c>
+      <c r="O36">
+        <v>-0.3702804799999999</v>
+      </c>
+      <c r="P36">
+        <v>-1.48112192</v>
+      </c>
+      <c r="Q36">
+        <v>4.078878079999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1212851858468185</v>
+      </c>
+      <c r="T36">
+        <v>1.249026488536791</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04644600171253046</v>
+      </c>
+      <c r="W36">
+        <v>0.2277086947910477</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2322300085626523</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1594691788878564</v>
+      </c>
+      <c r="C37">
+        <v>13.91039689579561</v>
+      </c>
+      <c r="D37">
+        <v>16.72539689579561</v>
+      </c>
+      <c r="E37">
+        <v>-7.504999999999997</v>
+      </c>
+      <c r="F37">
+        <v>10.395</v>
+      </c>
+      <c r="G37">
+        <v>7.58</v>
+      </c>
+      <c r="H37">
+        <v>11.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.12</v>
+      </c>
+      <c r="K37">
+        <v>5.56</v>
+      </c>
+      <c r="L37">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M37">
+        <v>2.482326</v>
+      </c>
+      <c r="N37">
+        <v>-1.922326</v>
+      </c>
+      <c r="O37">
+        <v>-0.3844651999999999</v>
+      </c>
+      <c r="P37">
+        <v>-1.5378608</v>
+      </c>
+      <c r="Q37">
+        <v>4.0221392</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1225541887060003</v>
+      </c>
+      <c r="T37">
+        <v>1.268242280668126</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04511897309217244</v>
+      </c>
+      <c r="W37">
+        <v>0.2280255892255892</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2255948654608623</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1614691788878564</v>
+      </c>
+      <c r="C38">
+        <v>13.49167137093725</v>
+      </c>
+      <c r="D38">
+        <v>16.60367137093725</v>
+      </c>
+      <c r="E38">
+        <v>-7.207999999999998</v>
+      </c>
+      <c r="F38">
+        <v>10.692</v>
+      </c>
+      <c r="G38">
+        <v>7.58</v>
+      </c>
+      <c r="H38">
+        <v>11.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.12</v>
+      </c>
+      <c r="K38">
+        <v>5.56</v>
+      </c>
+      <c r="L38">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M38">
+        <v>2.5532496</v>
+      </c>
+      <c r="N38">
+        <v>-1.9932496</v>
+      </c>
+      <c r="O38">
+        <v>-0.3986499199999998</v>
+      </c>
+      <c r="P38">
+        <v>-1.59459968</v>
+      </c>
+      <c r="Q38">
+        <v>3.96540032</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1238628479045316</v>
+      </c>
+      <c r="T38">
+        <v>1.288058566303566</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04386566828405655</v>
+      </c>
+      <c r="W38">
+        <v>0.2283248784137673</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2193283414202828</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1634691788878564</v>
+      </c>
+      <c r="C39">
+        <v>13.07470485311072</v>
+      </c>
+      <c r="D39">
+        <v>16.48370485311072</v>
+      </c>
+      <c r="E39">
+        <v>-6.911</v>
+      </c>
+      <c r="F39">
+        <v>10.989</v>
+      </c>
+      <c r="G39">
+        <v>7.58</v>
+      </c>
+      <c r="H39">
+        <v>11.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.12</v>
+      </c>
+      <c r="K39">
+        <v>5.56</v>
+      </c>
+      <c r="L39">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M39">
+        <v>2.6241732</v>
+      </c>
+      <c r="N39">
+        <v>-2.064173199999999</v>
+      </c>
+      <c r="O39">
+        <v>-0.4128346399999998</v>
+      </c>
+      <c r="P39">
+        <v>-1.65133856</v>
+      </c>
+      <c r="Q39">
+        <v>3.90866144</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1252130518395241</v>
+      </c>
+      <c r="T39">
+        <v>1.308503940371876</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04268010968178475</v>
+      </c>
+      <c r="W39">
+        <v>0.2286079898079898</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2134005484089239</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1654691788878564</v>
+      </c>
+      <c r="C40">
+        <v>12.65945948776251</v>
+      </c>
+      <c r="D40">
+        <v>16.36545948776251</v>
+      </c>
+      <c r="E40">
+        <v>-6.613999999999999</v>
+      </c>
+      <c r="F40">
+        <v>11.286</v>
+      </c>
+      <c r="G40">
+        <v>7.58</v>
+      </c>
+      <c r="H40">
+        <v>11.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.12</v>
+      </c>
+      <c r="K40">
+        <v>5.56</v>
+      </c>
+      <c r="L40">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M40">
+        <v>2.6950968</v>
+      </c>
+      <c r="N40">
+        <v>-2.135096799999999</v>
+      </c>
+      <c r="O40">
+        <v>-0.4270193599999998</v>
+      </c>
+      <c r="P40">
+        <v>-1.70807744</v>
+      </c>
+      <c r="Q40">
+        <v>3.85192256</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1266068107401616</v>
+      </c>
+      <c r="T40">
+        <v>1.329608842635939</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04155694890068515</v>
+      </c>
+      <c r="W40">
+        <v>0.2288762006025164</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2077847445034258</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1674691788878565</v>
+      </c>
+      <c r="C41">
+        <v>12.24589849879688</v>
+      </c>
+      <c r="D41">
+        <v>16.24889849879688</v>
+      </c>
+      <c r="E41">
+        <v>-6.316999999999998</v>
+      </c>
+      <c r="F41">
+        <v>11.583</v>
+      </c>
+      <c r="G41">
+        <v>7.58</v>
+      </c>
+      <c r="H41">
+        <v>11.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.12</v>
+      </c>
+      <c r="K41">
+        <v>5.56</v>
+      </c>
+      <c r="L41">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M41">
+        <v>2.7660204</v>
+      </c>
+      <c r="N41">
+        <v>-2.2060204</v>
+      </c>
+      <c r="O41">
+        <v>-0.4412040799999999</v>
+      </c>
+      <c r="P41">
+        <v>-1.76481632</v>
+      </c>
+      <c r="Q41">
+        <v>3.79518368</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1280462666539348</v>
+      </c>
+      <c r="T41">
+        <v>1.351405708908659</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04049138610835989</v>
+      </c>
+      <c r="W41">
+        <v>0.2291306569973237</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2024569305417995</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1694691788878565</v>
+      </c>
+      <c r="C42">
+        <v>11.83398615044152</v>
+      </c>
+      <c r="D42">
+        <v>16.13398615044152</v>
+      </c>
+      <c r="E42">
+        <v>-6.019999999999998</v>
+      </c>
+      <c r="F42">
+        <v>11.88</v>
+      </c>
+      <c r="G42">
+        <v>7.58</v>
+      </c>
+      <c r="H42">
+        <v>11.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.12</v>
+      </c>
+      <c r="K42">
+        <v>5.56</v>
+      </c>
+      <c r="L42">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M42">
+        <v>2.836944</v>
+      </c>
+      <c r="N42">
+        <v>-2.276944</v>
+      </c>
+      <c r="O42">
+        <v>-0.4553887999999999</v>
+      </c>
+      <c r="P42">
+        <v>-1.8215552</v>
+      </c>
+      <c r="Q42">
+        <v>3.7384448</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1295337044315004</v>
+      </c>
+      <c r="T42">
+        <v>1.37392913739047</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.03947910145565089</v>
+      </c>
+      <c r="W42">
+        <v>0.2293723905723906</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1973955072782545</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1714691788878565</v>
+      </c>
+      <c r="C43">
+        <v>11.42368771072002</v>
+      </c>
+      <c r="D43">
+        <v>16.02068771072003</v>
+      </c>
+      <c r="E43">
+        <v>-5.722999999999997</v>
+      </c>
+      <c r="F43">
+        <v>12.177</v>
+      </c>
+      <c r="G43">
+        <v>7.58</v>
+      </c>
+      <c r="H43">
+        <v>11.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.12</v>
+      </c>
+      <c r="K43">
+        <v>5.56</v>
+      </c>
+      <c r="L43">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M43">
+        <v>2.9078676</v>
+      </c>
+      <c r="N43">
+        <v>-2.3478676</v>
+      </c>
+      <c r="O43">
+        <v>-0.4695735199999999</v>
+      </c>
+      <c r="P43">
+        <v>-1.87829408</v>
+      </c>
+      <c r="Q43">
+        <v>3.68170592</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1310715638286444</v>
+      </c>
+      <c r="T43">
+        <v>1.397216071922512</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03851619654209843</v>
+      </c>
+      <c r="W43">
+        <v>0.2296023322657469</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1925809827104922</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1734691788878565</v>
+      </c>
+      <c r="C44">
+        <v>11.01496941645263</v>
+      </c>
+      <c r="D44">
+        <v>15.90896941645263</v>
+      </c>
+      <c r="E44">
+        <v>-5.426</v>
+      </c>
+      <c r="F44">
+        <v>12.474</v>
+      </c>
+      <c r="G44">
+        <v>7.58</v>
+      </c>
+      <c r="H44">
+        <v>11.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.12</v>
+      </c>
+      <c r="K44">
+        <v>5.56</v>
+      </c>
+      <c r="L44">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M44">
+        <v>2.9787912</v>
+      </c>
+      <c r="N44">
+        <v>-2.418791199999999</v>
+      </c>
+      <c r="O44">
+        <v>-0.4837582399999998</v>
+      </c>
+      <c r="P44">
+        <v>-1.93503296</v>
+      </c>
+      <c r="Q44">
+        <v>3.62496704</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1326624528601728</v>
+      </c>
+      <c r="T44">
+        <v>1.421306004197038</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03759914424347705</v>
+      </c>
+      <c r="W44">
+        <v>0.2298213243546577</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1879957212173853</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1754691788878565</v>
+      </c>
+      <c r="C45">
+        <v>10.60779843971123</v>
+      </c>
+      <c r="D45">
+        <v>15.79879843971123</v>
+      </c>
+      <c r="E45">
+        <v>-5.129</v>
+      </c>
+      <c r="F45">
+        <v>12.771</v>
+      </c>
+      <c r="G45">
+        <v>7.58</v>
+      </c>
+      <c r="H45">
+        <v>11.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.12</v>
+      </c>
+      <c r="K45">
+        <v>5.56</v>
+      </c>
+      <c r="L45">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M45">
+        <v>3.0497148</v>
+      </c>
+      <c r="N45">
+        <v>-2.489714799999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.4979429599999998</v>
+      </c>
+      <c r="P45">
+        <v>-1.99177184</v>
+      </c>
+      <c r="Q45">
+        <v>3.56822816</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1343091625594741</v>
+      </c>
+      <c r="T45">
+        <v>1.446241197253126</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03672474554014037</v>
+      </c>
+      <c r="W45">
+        <v>0.2300301307650145</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1836237277007019</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1774691788878564</v>
+      </c>
+      <c r="C46">
+        <v>10.20214285565862</v>
+      </c>
+      <c r="D46">
+        <v>15.69014285565862</v>
+      </c>
+      <c r="E46">
+        <v>-4.831999999999999</v>
+      </c>
+      <c r="F46">
+        <v>13.068</v>
+      </c>
+      <c r="G46">
+        <v>7.58</v>
+      </c>
+      <c r="H46">
+        <v>11.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.12</v>
+      </c>
+      <c r="K46">
+        <v>5.56</v>
+      </c>
+      <c r="L46">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M46">
+        <v>3.1206384</v>
+      </c>
+      <c r="N46">
+        <v>-2.5606384</v>
+      </c>
+      <c r="O46">
+        <v>-0.5121276799999999</v>
+      </c>
+      <c r="P46">
+        <v>-2.04851072</v>
+      </c>
+      <c r="Q46">
+        <v>3.51148928</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1360146833194646</v>
+      </c>
+      <c r="T46">
+        <v>1.472066932918361</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.0358900922324099</v>
+      </c>
+      <c r="W46">
+        <v>0.2302294459749005</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1794504611620495</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1794691788878565</v>
+      </c>
+      <c r="C47">
+        <v>9.797971611705696</v>
+      </c>
+      <c r="D47">
+        <v>15.5829716117057</v>
+      </c>
+      <c r="E47">
+        <v>-4.534999999999998</v>
+      </c>
+      <c r="F47">
+        <v>13.365</v>
+      </c>
+      <c r="G47">
+        <v>7.58</v>
+      </c>
+      <c r="H47">
+        <v>11.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.12</v>
+      </c>
+      <c r="K47">
+        <v>5.56</v>
+      </c>
+      <c r="L47">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M47">
+        <v>3.191562</v>
+      </c>
+      <c r="N47">
+        <v>-2.631562</v>
+      </c>
+      <c r="O47">
+        <v>-0.5263123999999998</v>
+      </c>
+      <c r="P47">
+        <v>-2.1052496</v>
+      </c>
+      <c r="Q47">
+        <v>3.4547504</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1377822230161822</v>
+      </c>
+      <c r="T47">
+        <v>1.498831786244149</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03509253462724524</v>
+      </c>
+      <c r="W47">
+        <v>0.2304199027310138</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1754626731362262</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1814691788878565</v>
+      </c>
+      <c r="C48">
+        <v>9.395254497924268</v>
+      </c>
+      <c r="D48">
+        <v>15.47725449792427</v>
+      </c>
+      <c r="E48">
+        <v>-4.237999999999998</v>
+      </c>
+      <c r="F48">
+        <v>13.662</v>
+      </c>
+      <c r="G48">
+        <v>7.58</v>
+      </c>
+      <c r="H48">
+        <v>11.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.12</v>
+      </c>
+      <c r="K48">
+        <v>5.56</v>
+      </c>
+      <c r="L48">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M48">
+        <v>3.2624856</v>
+      </c>
+      <c r="N48">
+        <v>-2.7024856</v>
+      </c>
+      <c r="O48">
+        <v>-0.5404971199999998</v>
+      </c>
+      <c r="P48">
+        <v>-2.16198848</v>
+      </c>
+      <c r="Q48">
+        <v>3.39801152</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1396152271461115</v>
+      </c>
+      <c r="T48">
+        <v>1.526587930433855</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03432965343969643</v>
+      </c>
+      <c r="W48">
+        <v>0.2306020787586005</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1716482671984821</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1834691788878565</v>
+      </c>
+      <c r="C49">
+        <v>8.993962118655949</v>
+      </c>
+      <c r="D49">
+        <v>15.37296211865595</v>
+      </c>
+      <c r="E49">
+        <v>-3.940999999999997</v>
+      </c>
+      <c r="F49">
+        <v>13.959</v>
+      </c>
+      <c r="G49">
+        <v>7.58</v>
+      </c>
+      <c r="H49">
+        <v>11.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.12</v>
+      </c>
+      <c r="K49">
+        <v>5.56</v>
+      </c>
+      <c r="L49">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M49">
+        <v>3.333409200000001</v>
+      </c>
+      <c r="N49">
+        <v>-2.7734092</v>
+      </c>
+      <c r="O49">
+        <v>-0.5546818399999999</v>
+      </c>
+      <c r="P49">
+        <v>-2.21872736</v>
+      </c>
+      <c r="Q49">
+        <v>3.341272639999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1415174012432079</v>
+      </c>
+      <c r="T49">
+        <v>1.555391476291098</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03359923528140502</v>
+      </c>
+      <c r="W49">
+        <v>0.2307765026148005</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1679961764070251</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1854691788878565</v>
+      </c>
+      <c r="C50">
+        <v>8.594065865261294</v>
+      </c>
+      <c r="D50">
+        <v>15.27006586526129</v>
+      </c>
+      <c r="E50">
+        <v>-3.644</v>
+      </c>
+      <c r="F50">
+        <v>14.256</v>
+      </c>
+      <c r="G50">
+        <v>7.58</v>
+      </c>
+      <c r="H50">
+        <v>11.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.12</v>
+      </c>
+      <c r="K50">
+        <v>5.56</v>
+      </c>
+      <c r="L50">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M50">
+        <v>3.4043328</v>
+      </c>
+      <c r="N50">
+        <v>-2.844332799999999</v>
+      </c>
+      <c r="O50">
+        <v>-0.5688665599999997</v>
+      </c>
+      <c r="P50">
+        <v>-2.27546624</v>
+      </c>
+      <c r="Q50">
+        <v>3.28453376</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1434927358825004</v>
+      </c>
+      <c r="T50">
+        <v>1.585302850835158</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03289925121304241</v>
+      </c>
+      <c r="W50">
+        <v>0.2309436588103255</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1644962560652121</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1874691788878564</v>
+      </c>
+      <c r="C51">
+        <v>8.195537889956045</v>
+      </c>
+      <c r="D51">
+        <v>15.16853788995604</v>
+      </c>
+      <c r="E51">
+        <v>-3.347</v>
+      </c>
+      <c r="F51">
+        <v>14.553</v>
+      </c>
+      <c r="G51">
+        <v>7.58</v>
+      </c>
+      <c r="H51">
+        <v>11.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.12</v>
+      </c>
+      <c r="K51">
+        <v>5.56</v>
+      </c>
+      <c r="L51">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M51">
+        <v>3.4752564</v>
+      </c>
+      <c r="N51">
+        <v>-2.9152564</v>
+      </c>
+      <c r="O51">
+        <v>-0.5830512799999998</v>
+      </c>
+      <c r="P51">
+        <v>-2.33220512</v>
+      </c>
+      <c r="Q51">
+        <v>3.22779488</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1455455346252945</v>
+      </c>
+      <c r="T51">
+        <v>1.616387220459376</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03222783792298032</v>
+      </c>
+      <c r="W51">
+        <v>0.2311039923039923</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1611391896149016</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1894691788878564</v>
+      </c>
+      <c r="C52">
+        <v>7.798351080684258</v>
+      </c>
+      <c r="D52">
+        <v>15.06835108068426</v>
+      </c>
+      <c r="E52">
+        <v>-3.049999999999999</v>
+      </c>
+      <c r="F52">
+        <v>14.85</v>
+      </c>
+      <c r="G52">
+        <v>7.58</v>
+      </c>
+      <c r="H52">
+        <v>11.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.12</v>
+      </c>
+      <c r="K52">
+        <v>5.56</v>
+      </c>
+      <c r="L52">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M52">
+        <v>3.54618</v>
+      </c>
+      <c r="N52">
+        <v>-2.98618</v>
+      </c>
+      <c r="O52">
+        <v>-0.5972359999999998</v>
+      </c>
+      <c r="P52">
+        <v>-2.388944</v>
+      </c>
+      <c r="Q52">
+        <v>3.171056</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1476804453178004</v>
+      </c>
+      <c r="T52">
+        <v>1.648714964868564</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03158328116452071</v>
+      </c>
+      <c r="W52">
+        <v>0.2312579124579125</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1579164058226036</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1914691788878565</v>
+      </c>
+      <c r="C53">
+        <v>7.402479036980624</v>
+      </c>
+      <c r="D53">
+        <v>14.96947903698062</v>
+      </c>
+      <c r="E53">
+        <v>-2.752999999999998</v>
+      </c>
+      <c r="F53">
+        <v>15.147</v>
+      </c>
+      <c r="G53">
+        <v>7.58</v>
+      </c>
+      <c r="H53">
+        <v>11.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.12</v>
+      </c>
+      <c r="K53">
+        <v>5.56</v>
+      </c>
+      <c r="L53">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M53">
+        <v>3.6171036</v>
+      </c>
+      <c r="N53">
+        <v>-3.0571036</v>
+      </c>
+      <c r="O53">
+        <v>-0.6114207199999998</v>
+      </c>
+      <c r="P53">
+        <v>-2.44568288</v>
+      </c>
+      <c r="Q53">
+        <v>3.11431712</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1499024952222454</v>
+      </c>
+      <c r="T53">
+        <v>1.682362209049555</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03096400114168697</v>
+      </c>
+      <c r="W53">
+        <v>0.2314057965273652</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1548200057084349</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1934691788878564</v>
+      </c>
+      <c r="C54">
+        <v>7.00789604677689</v>
+      </c>
+      <c r="D54">
+        <v>14.87189604677689</v>
+      </c>
+      <c r="E54">
+        <v>-2.455999999999998</v>
+      </c>
+      <c r="F54">
+        <v>15.444</v>
+      </c>
+      <c r="G54">
+        <v>7.58</v>
+      </c>
+      <c r="H54">
+        <v>11.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.12</v>
+      </c>
+      <c r="K54">
+        <v>5.56</v>
+      </c>
+      <c r="L54">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M54">
+        <v>3.688027200000001</v>
+      </c>
+      <c r="N54">
+        <v>-3.1280272</v>
+      </c>
+      <c r="O54">
+        <v>-0.6256054399999998</v>
+      </c>
+      <c r="P54">
+        <v>-2.50242176</v>
+      </c>
+      <c r="Q54">
+        <v>3.057578239999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1522171305393754</v>
+      </c>
+      <c r="T54">
+        <v>1.717411421738088</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03036853958126991</v>
+      </c>
+      <c r="W54">
+        <v>0.2315479927479928</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1518426979063496</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1954691788878564</v>
+      </c>
+      <c r="C55">
+        <v>6.614577064109589</v>
+      </c>
+      <c r="D55">
+        <v>14.77557706410959</v>
+      </c>
+      <c r="E55">
+        <v>-2.158999999999999</v>
+      </c>
+      <c r="F55">
+        <v>15.741</v>
+      </c>
+      <c r="G55">
+        <v>7.58</v>
+      </c>
+      <c r="H55">
+        <v>11.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.12</v>
+      </c>
+      <c r="K55">
+        <v>5.56</v>
+      </c>
+      <c r="L55">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M55">
+        <v>3.7589508</v>
+      </c>
+      <c r="N55">
+        <v>-3.1989508</v>
+      </c>
+      <c r="O55">
+        <v>-0.6397901599999998</v>
+      </c>
+      <c r="P55">
+        <v>-2.55916064</v>
+      </c>
+      <c r="Q55">
+        <v>3.00083936</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1546302609763834</v>
+      </c>
+      <c r="T55">
+        <v>1.753952090285707</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02979554826841577</v>
+      </c>
+      <c r="W55">
+        <v>0.2316848230735023</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1489777413420789</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1974691788878564</v>
+      </c>
+      <c r="C56">
+        <v>6.222497687688428</v>
+      </c>
+      <c r="D56">
+        <v>14.68049768768843</v>
+      </c>
+      <c r="E56">
+        <v>-1.861999999999998</v>
+      </c>
+      <c r="F56">
+        <v>16.038</v>
+      </c>
+      <c r="G56">
+        <v>7.58</v>
+      </c>
+      <c r="H56">
+        <v>11.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.12</v>
+      </c>
+      <c r="K56">
+        <v>5.56</v>
+      </c>
+      <c r="L56">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M56">
+        <v>3.8298744</v>
+      </c>
+      <c r="N56">
+        <v>-3.2698744</v>
+      </c>
+      <c r="O56">
+        <v>-0.6539748799999998</v>
+      </c>
+      <c r="P56">
+        <v>-2.61589952</v>
+      </c>
+      <c r="Q56">
+        <v>2.944100479999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1571483101280439</v>
+      </c>
+      <c r="T56">
+        <v>1.792081483552787</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0292437788560377</v>
+      </c>
+      <c r="W56">
+        <v>0.2318165856091782</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1462188942801885</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1994691788878565</v>
+      </c>
+      <c r="C57">
+        <v>5.831634140286891</v>
+      </c>
+      <c r="D57">
+        <v>14.58663414028689</v>
+      </c>
+      <c r="E57">
+        <v>-1.564999999999998</v>
+      </c>
+      <c r="F57">
+        <v>16.335</v>
+      </c>
+      <c r="G57">
+        <v>7.58</v>
+      </c>
+      <c r="H57">
+        <v>11.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.12</v>
+      </c>
+      <c r="K57">
+        <v>5.56</v>
+      </c>
+      <c r="L57">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M57">
+        <v>3.900798</v>
+      </c>
+      <c r="N57">
+        <v>-3.340798</v>
+      </c>
+      <c r="O57">
+        <v>-0.6681595999999999</v>
+      </c>
+      <c r="P57">
+        <v>-2.6726384</v>
+      </c>
+      <c r="Q57">
+        <v>2.887361599999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1597782725753338</v>
+      </c>
+      <c r="T57">
+        <v>1.831905516520627</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02871207378592792</v>
+      </c>
+      <c r="W57">
+        <v>0.2319435567799204</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1435603689296396</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2014691788878565</v>
+      </c>
+      <c r="C58">
+        <v>5.441963248918412</v>
+      </c>
+      <c r="D58">
+        <v>14.49396324891841</v>
+      </c>
+      <c r="E58">
+        <v>-1.267999999999997</v>
+      </c>
+      <c r="F58">
+        <v>16.632</v>
+      </c>
+      <c r="G58">
+        <v>7.58</v>
+      </c>
+      <c r="H58">
+        <v>11.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.12</v>
+      </c>
+      <c r="K58">
+        <v>5.56</v>
+      </c>
+      <c r="L58">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M58">
+        <v>3.9717216</v>
+      </c>
+      <c r="N58">
+        <v>-3.4117216</v>
+      </c>
+      <c r="O58">
+        <v>-0.6823443199999998</v>
+      </c>
+      <c r="P58">
+        <v>-2.72937728</v>
+      </c>
+      <c r="Q58">
+        <v>2.83062272</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1625277787702278</v>
+      </c>
+      <c r="T58">
+        <v>1.873539732805187</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02819935818260778</v>
+      </c>
+      <c r="W58">
+        <v>0.2320659932659933</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.140996790913039</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2034691788878565</v>
+      </c>
+      <c r="C59">
+        <v>5.053462425763449</v>
+      </c>
+      <c r="D59">
+        <v>14.40246242576345</v>
+      </c>
+      <c r="E59">
+        <v>-0.9709999999999965</v>
+      </c>
+      <c r="F59">
+        <v>16.929</v>
+      </c>
+      <c r="G59">
+        <v>7.58</v>
+      </c>
+      <c r="H59">
+        <v>11.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.12</v>
+      </c>
+      <c r="K59">
+        <v>5.56</v>
+      </c>
+      <c r="L59">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M59">
+        <v>4.042645200000001</v>
+      </c>
+      <c r="N59">
+        <v>-3.4826452</v>
+      </c>
+      <c r="O59">
+        <v>-0.6965290399999999</v>
+      </c>
+      <c r="P59">
+        <v>-2.786116160000001</v>
+      </c>
+      <c r="Q59">
+        <v>2.773883839999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1654051689741866</v>
+      </c>
+      <c r="T59">
+        <v>1.917110424265773</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02770463260045676</v>
+      </c>
+      <c r="W59">
+        <v>0.2321841337350109</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1385231630022838</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2054691788878564</v>
+      </c>
+      <c r="C60">
+        <v>4.666109649814494</v>
+      </c>
+      <c r="D60">
+        <v>14.31210964981449</v>
+      </c>
+      <c r="E60">
+        <v>-0.6739999999999995</v>
+      </c>
+      <c r="F60">
+        <v>17.226</v>
+      </c>
+      <c r="G60">
+        <v>7.58</v>
+      </c>
+      <c r="H60">
+        <v>11.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.12</v>
+      </c>
+      <c r="K60">
+        <v>5.56</v>
+      </c>
+      <c r="L60">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M60">
+        <v>4.1135688</v>
+      </c>
+      <c r="N60">
+        <v>-3.5535688</v>
+      </c>
+      <c r="O60">
+        <v>-0.7107137599999999</v>
+      </c>
+      <c r="P60">
+        <v>-2.84285504</v>
+      </c>
+      <c r="Q60">
+        <v>2.71714496</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1684195777592862</v>
+      </c>
+      <c r="T60">
+        <v>1.962755910557814</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02722696652113854</v>
+      </c>
+      <c r="W60">
+        <v>0.2322982003947521</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1361348326056928</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2074691788878564</v>
+      </c>
+      <c r="C61">
+        <v>4.279883449207592</v>
+      </c>
+      <c r="D61">
+        <v>14.22288344920759</v>
+      </c>
+      <c r="E61">
+        <v>-0.3769999999999989</v>
+      </c>
+      <c r="F61">
+        <v>17.523</v>
+      </c>
+      <c r="G61">
+        <v>7.58</v>
+      </c>
+      <c r="H61">
+        <v>11.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.12</v>
+      </c>
+      <c r="K61">
+        <v>5.56</v>
+      </c>
+      <c r="L61">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M61">
+        <v>4.1844924</v>
+      </c>
+      <c r="N61">
+        <v>-3.624492399999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.7248984799999997</v>
+      </c>
+      <c r="P61">
+        <v>-2.89959392</v>
+      </c>
+      <c r="Q61">
+        <v>2.66040608</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1715810308753664</v>
+      </c>
+      <c r="T61">
+        <v>2.010628005937273</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02676549251230569</v>
+      </c>
+      <c r="W61">
+        <v>0.2324084003880614</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1338274625615284</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2094691788878564</v>
+      </c>
+      <c r="C62">
+        <v>3.894762884210806</v>
+      </c>
+      <c r="D62">
+        <v>14.13476288421081</v>
+      </c>
+      <c r="E62">
+        <v>-0.07999999999999829</v>
+      </c>
+      <c r="F62">
+        <v>17.82</v>
+      </c>
+      <c r="G62">
+        <v>7.58</v>
+      </c>
+      <c r="H62">
+        <v>11.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.12</v>
+      </c>
+      <c r="K62">
+        <v>5.56</v>
+      </c>
+      <c r="L62">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M62">
+        <v>4.255416</v>
+      </c>
+      <c r="N62">
+        <v>-3.695416</v>
+      </c>
+      <c r="O62">
+        <v>-0.7390831999999998</v>
+      </c>
+      <c r="P62">
+        <v>-2.9563328</v>
+      </c>
+      <c r="Q62">
+        <v>2.603667199999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1749005566472505</v>
+      </c>
+      <c r="T62">
+        <v>2.060893706085705</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02631940097043393</v>
+      </c>
+      <c r="W62">
+        <v>0.2325149270482604</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1315970048521696</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2114691788878564</v>
+      </c>
+      <c r="C63">
+        <v>3.510727530841056</v>
+      </c>
+      <c r="D63">
+        <v>14.04772753084105</v>
+      </c>
+      <c r="E63">
+        <v>0.2170000000000023</v>
+      </c>
+      <c r="F63">
+        <v>18.117</v>
+      </c>
+      <c r="G63">
+        <v>7.58</v>
+      </c>
+      <c r="H63">
+        <v>11.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.12</v>
+      </c>
+      <c r="K63">
+        <v>5.56</v>
+      </c>
+      <c r="L63">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M63">
+        <v>4.326339600000001</v>
+      </c>
+      <c r="N63">
+        <v>-3.7663396</v>
+      </c>
+      <c r="O63">
+        <v>-0.7532679199999999</v>
+      </c>
+      <c r="P63">
+        <v>-3.01307168</v>
+      </c>
+      <c r="Q63">
+        <v>2.546928319999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1783903145100005</v>
+      </c>
+      <c r="T63">
+        <v>2.113737134446877</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02588793538075469</v>
+      </c>
+      <c r="W63">
+        <v>0.2326179610310758</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1294396769037734</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2134691788878564</v>
+      </c>
+      <c r="C64">
+        <v>3.127757465082571</v>
+      </c>
+      <c r="D64">
+        <v>13.96175746508257</v>
+      </c>
+      <c r="E64">
+        <v>0.5139999999999993</v>
+      </c>
+      <c r="F64">
+        <v>18.414</v>
+      </c>
+      <c r="G64">
+        <v>7.58</v>
+      </c>
+      <c r="H64">
+        <v>11.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.12</v>
+      </c>
+      <c r="K64">
+        <v>5.56</v>
+      </c>
+      <c r="L64">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M64">
+        <v>4.397263199999999</v>
+      </c>
+      <c r="N64">
+        <v>-3.837263199999999</v>
+      </c>
+      <c r="O64">
+        <v>-0.7674526399999996</v>
+      </c>
+      <c r="P64">
+        <v>-3.069810559999999</v>
+      </c>
+      <c r="Q64">
+        <v>2.49018944</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1820637438392111</v>
+      </c>
+      <c r="T64">
+        <v>2.169361795879689</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02547038803590381</v>
+      </c>
+      <c r="W64">
+        <v>0.2327176713370262</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1273519401795191</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2154691788878564</v>
+      </c>
+      <c r="C65">
+        <v>2.745833247681311</v>
+      </c>
+      <c r="D65">
+        <v>13.87683324768131</v>
+      </c>
+      <c r="E65">
+        <v>0.8109999999999999</v>
+      </c>
+      <c r="F65">
+        <v>18.711</v>
+      </c>
+      <c r="G65">
+        <v>7.58</v>
+      </c>
+      <c r="H65">
+        <v>11.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.12</v>
+      </c>
+      <c r="K65">
+        <v>5.56</v>
+      </c>
+      <c r="L65">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M65">
+        <v>4.4681868</v>
+      </c>
+      <c r="N65">
+        <v>-3.908186799999999</v>
+      </c>
+      <c r="O65">
+        <v>-0.7816373599999997</v>
+      </c>
+      <c r="P65">
+        <v>-3.12654944</v>
+      </c>
+      <c r="Q65">
+        <v>2.43345056</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1859357369159465</v>
+      </c>
+      <c r="T65">
+        <v>2.22799319576833</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02506609616231803</v>
+      </c>
+      <c r="W65">
+        <v>0.2328142162364385</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1253304808115902</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2174691788878564</v>
+      </c>
+      <c r="C66">
+        <v>2.364935909490999</v>
+      </c>
+      <c r="D66">
+        <v>13.792935909491</v>
+      </c>
+      <c r="E66">
+        <v>1.108000000000001</v>
+      </c>
+      <c r="F66">
+        <v>19.008</v>
+      </c>
+      <c r="G66">
+        <v>7.58</v>
+      </c>
+      <c r="H66">
+        <v>11.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.12</v>
+      </c>
+      <c r="K66">
+        <v>5.56</v>
+      </c>
+      <c r="L66">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M66">
+        <v>4.5391104</v>
+      </c>
+      <c r="N66">
+        <v>-3.9791104</v>
+      </c>
+      <c r="O66">
+        <v>-0.7958220799999998</v>
+      </c>
+      <c r="P66">
+        <v>-3.18328832</v>
+      </c>
+      <c r="Q66">
+        <v>2.37671168</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1900228407191673</v>
+      </c>
+      <c r="T66">
+        <v>2.289881895650784</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02467443840978181</v>
+      </c>
+      <c r="W66">
+        <v>0.2329077441077441</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.123372192048909</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2194691788878564</v>
+      </c>
+      <c r="C67">
+        <v>1.985046937347448</v>
+      </c>
+      <c r="D67">
+        <v>13.71004693734745</v>
+      </c>
+      <c r="E67">
+        <v>1.405000000000001</v>
+      </c>
+      <c r="F67">
+        <v>19.305</v>
+      </c>
+      <c r="G67">
+        <v>7.58</v>
+      </c>
+      <c r="H67">
+        <v>11.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.12</v>
+      </c>
+      <c r="K67">
+        <v>5.56</v>
+      </c>
+      <c r="L67">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M67">
+        <v>4.610034</v>
+      </c>
+      <c r="N67">
+        <v>-4.050033999999999</v>
+      </c>
+      <c r="O67">
+        <v>-0.8100067999999997</v>
+      </c>
+      <c r="P67">
+        <v>-3.2400272</v>
+      </c>
+      <c r="Q67">
+        <v>2.3199728</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1943434933111435</v>
+      </c>
+      <c r="T67">
+        <v>2.355307092669377</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02429483166501594</v>
+      </c>
+      <c r="W67">
+        <v>0.2329983941983942</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1214741583250797</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2214691788878564</v>
+      </c>
+      <c r="C68">
+        <v>1.606148260449281</v>
+      </c>
+      <c r="D68">
+        <v>13.62814826044928</v>
+      </c>
+      <c r="E68">
+        <v>1.702000000000002</v>
+      </c>
+      <c r="F68">
+        <v>19.602</v>
+      </c>
+      <c r="G68">
+        <v>7.58</v>
+      </c>
+      <c r="H68">
+        <v>11.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.12</v>
+      </c>
+      <c r="K68">
+        <v>5.56</v>
+      </c>
+      <c r="L68">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M68">
+        <v>4.6809576</v>
+      </c>
+      <c r="N68">
+        <v>-4.1209576</v>
+      </c>
+      <c r="O68">
+        <v>-0.8241915199999997</v>
+      </c>
+      <c r="P68">
+        <v>-3.29676608</v>
+      </c>
+      <c r="Q68">
+        <v>2.26323392</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1989183019379418</v>
+      </c>
+      <c r="T68">
+        <v>2.424580830689065</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02392672815493994</v>
+      </c>
+      <c r="W68">
+        <v>0.2330862973166004</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1196336407746997</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2234691788878564</v>
+      </c>
+      <c r="C69">
+        <v>1.228222237223811</v>
+      </c>
+      <c r="D69">
+        <v>13.54722223722381</v>
+      </c>
+      <c r="E69">
+        <v>1.999000000000002</v>
+      </c>
+      <c r="F69">
+        <v>19.899</v>
+      </c>
+      <c r="G69">
+        <v>7.58</v>
+      </c>
+      <c r="H69">
+        <v>11.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.12</v>
+      </c>
+      <c r="K69">
+        <v>5.56</v>
+      </c>
+      <c r="L69">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M69">
+        <v>4.751881200000001</v>
+      </c>
+      <c r="N69">
+        <v>-4.1918812</v>
+      </c>
+      <c r="O69">
+        <v>-0.8383762399999999</v>
+      </c>
+      <c r="P69">
+        <v>-3.35350496</v>
+      </c>
+      <c r="Q69">
+        <v>2.206495039999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.203770371693637</v>
+      </c>
+      <c r="T69">
+        <v>2.498052977073582</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02356961280934381</v>
+      </c>
+      <c r="W69">
+        <v>0.2331715764611287</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1178480640467191</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2254691788878564</v>
+      </c>
+      <c r="C70">
+        <v>0.8512516426581591</v>
+      </c>
+      <c r="D70">
+        <v>13.46725164265816</v>
+      </c>
+      <c r="E70">
+        <v>2.296000000000003</v>
+      </c>
+      <c r="F70">
+        <v>20.196</v>
+      </c>
+      <c r="G70">
+        <v>7.58</v>
+      </c>
+      <c r="H70">
+        <v>11.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.12</v>
+      </c>
+      <c r="K70">
+        <v>5.56</v>
+      </c>
+      <c r="L70">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M70">
+        <v>4.822804800000001</v>
+      </c>
+      <c r="N70">
+        <v>-4.262804800000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.8525609599999999</v>
+      </c>
+      <c r="P70">
+        <v>-3.410243840000001</v>
+      </c>
+      <c r="Q70">
+        <v>2.149756159999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2089256958090632</v>
+      </c>
+      <c r="T70">
+        <v>2.576117132607131</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02322300085626523</v>
+      </c>
+      <c r="W70">
+        <v>0.2332543473955239</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1161150042813262</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2274691788878564</v>
+      </c>
+      <c r="C71">
+        <v>0.4752196560764261</v>
+      </c>
+      <c r="D71">
+        <v>13.38821965607643</v>
+      </c>
+      <c r="E71">
+        <v>2.593000000000004</v>
+      </c>
+      <c r="F71">
+        <v>20.493</v>
+      </c>
+      <c r="G71">
+        <v>7.58</v>
+      </c>
+      <c r="H71">
+        <v>11.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.12</v>
+      </c>
+      <c r="K71">
+        <v>5.56</v>
+      </c>
+      <c r="L71">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M71">
+        <v>4.893728400000001</v>
+      </c>
+      <c r="N71">
+        <v>-4.3337284</v>
+      </c>
+      <c r="O71">
+        <v>-0.8667456799999999</v>
+      </c>
+      <c r="P71">
+        <v>-3.46698272</v>
+      </c>
+      <c r="Q71">
+        <v>2.093017279999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2144136214803233</v>
+      </c>
+      <c r="T71">
+        <v>2.659217685271878</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02288643562646429</v>
+      </c>
+      <c r="W71">
+        <v>0.2333347191724003</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1144321781323214</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2294691788878565</v>
+      </c>
+      <c r="C72">
+        <v>0.1001098493447579</v>
+      </c>
+      <c r="D72">
+        <v>13.31010984934476</v>
+      </c>
+      <c r="E72">
+        <v>2.890000000000004</v>
+      </c>
+      <c r="F72">
+        <v>20.79</v>
+      </c>
+      <c r="G72">
+        <v>7.58</v>
+      </c>
+      <c r="H72">
+        <v>11.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.12</v>
+      </c>
+      <c r="K72">
+        <v>5.56</v>
+      </c>
+      <c r="L72">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M72">
+        <v>4.964652000000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.404652</v>
+      </c>
+      <c r="O72">
+        <v>-0.8809303999999999</v>
+      </c>
+      <c r="P72">
+        <v>-3.5237216</v>
+      </c>
+      <c r="Q72">
+        <v>2.036278399999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2202674088630007</v>
+      </c>
+      <c r="T72">
+        <v>2.747858274780941</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02255948654608622</v>
+      </c>
+      <c r="W72">
+        <v>0.2334127946127946</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1127974327304311</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2314691788878565</v>
+      </c>
+      <c r="C73">
+        <v>-0.2740938245131339</v>
+      </c>
+      <c r="D73">
+        <v>13.23290617548687</v>
+      </c>
+      <c r="E73">
+        <v>3.187000000000001</v>
+      </c>
+      <c r="F73">
+        <v>21.087</v>
+      </c>
+      <c r="G73">
+        <v>7.58</v>
+      </c>
+      <c r="H73">
+        <v>11.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.12</v>
+      </c>
+      <c r="K73">
+        <v>5.56</v>
+      </c>
+      <c r="L73">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M73">
+        <v>5.0355756</v>
+      </c>
+      <c r="N73">
+        <v>-4.4755756</v>
+      </c>
+      <c r="O73">
+        <v>-0.8951151199999998</v>
+      </c>
+      <c r="P73">
+        <v>-3.58046048</v>
+      </c>
+      <c r="Q73">
+        <v>1.979539519999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2265249057203456</v>
+      </c>
+      <c r="T73">
+        <v>2.842612008394076</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02224174729895825</v>
+      </c>
+      <c r="W73">
+        <v>0.2334886707450088</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1112087364947912</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2334691788878564</v>
+      </c>
+      <c r="C74">
+        <v>-0.6474070423065115</v>
+      </c>
+      <c r="D74">
+        <v>13.15659295769349</v>
+      </c>
+      <c r="E74">
+        <v>3.484000000000002</v>
+      </c>
+      <c r="F74">
+        <v>21.384</v>
+      </c>
+      <c r="G74">
+        <v>7.58</v>
+      </c>
+      <c r="H74">
+        <v>11.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.12</v>
+      </c>
+      <c r="K74">
+        <v>5.56</v>
+      </c>
+      <c r="L74">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M74">
+        <v>5.1064992</v>
+      </c>
+      <c r="N74">
+        <v>-4.5464992</v>
+      </c>
+      <c r="O74">
+        <v>-0.9092998399999997</v>
+      </c>
+      <c r="P74">
+        <v>-3.63719936</v>
+      </c>
+      <c r="Q74">
+        <v>1.92280064</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2332293666389293</v>
+      </c>
+      <c r="T74">
+        <v>2.944133865836721</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02193283414202827</v>
+      </c>
+      <c r="W74">
+        <v>0.2335624392068837</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1096641707101415</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2354691788878564</v>
+      </c>
+      <c r="C75">
+        <v>-1.019845121290032</v>
+      </c>
+      <c r="D75">
+        <v>13.08115487870997</v>
+      </c>
+      <c r="E75">
+        <v>3.780999999999999</v>
+      </c>
+      <c r="F75">
+        <v>21.681</v>
+      </c>
+      <c r="G75">
+        <v>7.58</v>
+      </c>
+      <c r="H75">
+        <v>11.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.12</v>
+      </c>
+      <c r="K75">
+        <v>5.56</v>
+      </c>
+      <c r="L75">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M75">
+        <v>5.1774228</v>
+      </c>
+      <c r="N75">
+        <v>-4.617422799999999</v>
+      </c>
+      <c r="O75">
+        <v>-0.9234845599999996</v>
+      </c>
+      <c r="P75">
+        <v>-3.69393824</v>
+      </c>
+      <c r="Q75">
+        <v>1.86606176</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.240430454292223</v>
+      </c>
+      <c r="T75">
+        <v>3.053175860867711</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02163238435926076</v>
+      </c>
+      <c r="W75">
+        <v>0.2336341866150085</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1081619217963039</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2374691788878564</v>
+      </c>
+      <c r="C76">
+        <v>-1.391423029413168</v>
+      </c>
+      <c r="D76">
+        <v>13.00657697058683</v>
+      </c>
+      <c r="E76">
+        <v>4.077999999999999</v>
+      </c>
+      <c r="F76">
+        <v>21.978</v>
+      </c>
+      <c r="G76">
+        <v>7.58</v>
+      </c>
+      <c r="H76">
+        <v>11.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.12</v>
+      </c>
+      <c r="K76">
+        <v>5.56</v>
+      </c>
+      <c r="L76">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M76">
+        <v>5.2483464</v>
+      </c>
+      <c r="N76">
+        <v>-4.688346399999999</v>
+      </c>
+      <c r="O76">
+        <v>-0.9376692799999997</v>
+      </c>
+      <c r="P76">
+        <v>-3.75067712</v>
+      </c>
+      <c r="Q76">
+        <v>1.80932288</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2481854717650008</v>
+      </c>
+      <c r="T76">
+        <v>3.170605701670315</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02134005484089238</v>
+      </c>
+      <c r="W76">
+        <v>0.2337039949039949</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1067002742044619</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2394691788878564</v>
+      </c>
+      <c r="C77">
+        <v>-1.762155395221008</v>
+      </c>
+      <c r="D77">
+        <v>12.93284460477899</v>
+      </c>
+      <c r="E77">
+        <v>4.375</v>
+      </c>
+      <c r="F77">
+        <v>22.275</v>
+      </c>
+      <c r="G77">
+        <v>7.58</v>
+      </c>
+      <c r="H77">
+        <v>11.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.12</v>
+      </c>
+      <c r="K77">
+        <v>5.56</v>
+      </c>
+      <c r="L77">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M77">
+        <v>5.319269999999999</v>
+      </c>
+      <c r="N77">
+        <v>-4.759269999999999</v>
+      </c>
+      <c r="O77">
+        <v>-0.9518539999999995</v>
+      </c>
+      <c r="P77">
+        <v>-3.807415999999999</v>
+      </c>
+      <c r="Q77">
+        <v>1.752584</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2565608906356008</v>
+      </c>
+      <c r="T77">
+        <v>3.297429929737128</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02105552077634714</v>
+      </c>
+      <c r="W77">
+        <v>0.2337719416386083</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1052776038817358</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2414691788878565</v>
+      </c>
+      <c r="C78">
+        <v>-2.132056517420182</v>
+      </c>
+      <c r="D78">
+        <v>12.85994348257982</v>
+      </c>
+      <c r="E78">
+        <v>4.672000000000001</v>
+      </c>
+      <c r="F78">
+        <v>22.572</v>
+      </c>
+      <c r="G78">
+        <v>7.58</v>
+      </c>
+      <c r="H78">
+        <v>11.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.12</v>
+      </c>
+      <c r="K78">
+        <v>5.56</v>
+      </c>
+      <c r="L78">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M78">
+        <v>5.3901936</v>
+      </c>
+      <c r="N78">
+        <v>-4.830193599999999</v>
+      </c>
+      <c r="O78">
+        <v>-0.9660387199999997</v>
+      </c>
+      <c r="P78">
+        <v>-3.86415488</v>
+      </c>
+      <c r="Q78">
+        <v>1.69584512</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2656342610787509</v>
+      </c>
+      <c r="T78">
+        <v>3.434822843476175</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02077847445034258</v>
+      </c>
+      <c r="W78">
+        <v>0.2338381003012582</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1038923722517129</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2434691788878565</v>
+      </c>
+      <c r="C79">
+        <v>-2.501140374123096</v>
+      </c>
+      <c r="D79">
+        <v>12.7878596258769</v>
+      </c>
+      <c r="E79">
+        <v>4.969000000000001</v>
+      </c>
+      <c r="F79">
+        <v>22.869</v>
+      </c>
+      <c r="G79">
+        <v>7.58</v>
+      </c>
+      <c r="H79">
+        <v>11.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.12</v>
+      </c>
+      <c r="K79">
+        <v>5.56</v>
+      </c>
+      <c r="L79">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M79">
+        <v>5.4611172</v>
+      </c>
+      <c r="N79">
+        <v>-4.9011172</v>
+      </c>
+      <c r="O79">
+        <v>-0.9802234399999997</v>
+      </c>
+      <c r="P79">
+        <v>-3.92089376</v>
+      </c>
+      <c r="Q79">
+        <v>1.639106239999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2754966202560879</v>
+      </c>
+      <c r="T79">
+        <v>3.584162967105574</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02050862413280566</v>
+      </c>
+      <c r="W79">
+        <v>0.233902540557086</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1025431206640283</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2454691788878565</v>
+      </c>
+      <c r="C80">
+        <v>-2.869420631782976</v>
+      </c>
+      <c r="D80">
+        <v>12.71657936821703</v>
+      </c>
+      <c r="E80">
+        <v>5.266000000000002</v>
+      </c>
+      <c r="F80">
+        <v>23.166</v>
+      </c>
+      <c r="G80">
+        <v>7.58</v>
+      </c>
+      <c r="H80">
+        <v>11.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.12</v>
+      </c>
+      <c r="K80">
+        <v>5.56</v>
+      </c>
+      <c r="L80">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M80">
+        <v>5.532040800000001</v>
+      </c>
+      <c r="N80">
+        <v>-4.9720408</v>
+      </c>
+      <c r="O80">
+        <v>-0.9944081599999999</v>
+      </c>
+      <c r="P80">
+        <v>-3.97763264</v>
+      </c>
+      <c r="Q80">
+        <v>1.582367359999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2862555575404555</v>
+      </c>
+      <c r="T80">
+        <v>3.747079465610373</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02024569305417994</v>
+      </c>
+      <c r="W80">
+        <v>0.2339653284986619</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1012284652708998</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2474691788878565</v>
+      </c>
+      <c r="C81">
+        <v>-3.236910653831753</v>
+      </c>
+      <c r="D81">
+        <v>12.64608934616825</v>
+      </c>
+      <c r="E81">
+        <v>5.563000000000002</v>
+      </c>
+      <c r="F81">
+        <v>23.463</v>
+      </c>
+      <c r="G81">
+        <v>7.58</v>
+      </c>
+      <c r="H81">
+        <v>11.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.12</v>
+      </c>
+      <c r="K81">
+        <v>5.56</v>
+      </c>
+      <c r="L81">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M81">
+        <v>5.6029644</v>
+      </c>
+      <c r="N81">
+        <v>-5.0429644</v>
+      </c>
+      <c r="O81">
+        <v>-1.00859288</v>
+      </c>
+      <c r="P81">
+        <v>-4.034371520000001</v>
+      </c>
+      <c r="Q81">
+        <v>1.525628479999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2980391555185725</v>
+      </c>
+      <c r="T81">
+        <v>3.925511821115629</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01998941845855742</v>
+      </c>
+      <c r="W81">
+        <v>0.2340265268720965</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.09994709229278709</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2494691788878565</v>
+      </c>
+      <c r="C82">
+        <v>-3.603623509032239</v>
+      </c>
+      <c r="D82">
+        <v>12.57637649096776</v>
+      </c>
+      <c r="E82">
+        <v>5.860000000000003</v>
+      </c>
+      <c r="F82">
+        <v>23.76</v>
+      </c>
+      <c r="G82">
+        <v>7.58</v>
+      </c>
+      <c r="H82">
+        <v>11.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.12</v>
+      </c>
+      <c r="K82">
+        <v>5.56</v>
+      </c>
+      <c r="L82">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M82">
+        <v>5.673888000000001</v>
+      </c>
+      <c r="N82">
+        <v>-5.113888</v>
+      </c>
+      <c r="O82">
+        <v>-1.0227776</v>
+      </c>
+      <c r="P82">
+        <v>-4.091110400000001</v>
+      </c>
+      <c r="Q82">
+        <v>1.468889599999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3110011132945011</v>
+      </c>
+      <c r="T82">
+        <v>4.121787412171411</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01973955072782545</v>
+      </c>
+      <c r="W82">
+        <v>0.2340861952861953</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.09869775363912725</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2514691788878565</v>
+      </c>
+      <c r="C83">
+        <v>-3.969571979555582</v>
+      </c>
+      <c r="D83">
+        <v>12.50742802044442</v>
+      </c>
+      <c r="E83">
+        <v>6.157000000000004</v>
+      </c>
+      <c r="F83">
+        <v>24.057</v>
+      </c>
+      <c r="G83">
+        <v>7.58</v>
+      </c>
+      <c r="H83">
+        <v>11.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.12</v>
+      </c>
+      <c r="K83">
+        <v>5.56</v>
+      </c>
+      <c r="L83">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M83">
+        <v>5.744811600000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.184811600000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.03696232</v>
+      </c>
+      <c r="P83">
+        <v>-4.147849280000001</v>
+      </c>
+      <c r="Q83">
+        <v>1.412150719999999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3253274876784222</v>
+      </c>
+      <c r="T83">
+        <v>4.33872359175938</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0194958525706918</v>
+      </c>
+      <c r="W83">
+        <v>0.2341443904061188</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09747926285345898</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2534691788878565</v>
+      </c>
+      <c r="C84">
+        <v>-4.334768568794413</v>
+      </c>
+      <c r="D84">
+        <v>12.43923143120559</v>
+      </c>
+      <c r="E84">
+        <v>6.454000000000004</v>
+      </c>
+      <c r="F84">
+        <v>24.354</v>
+      </c>
+      <c r="G84">
+        <v>7.58</v>
+      </c>
+      <c r="H84">
+        <v>11.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.12</v>
+      </c>
+      <c r="K84">
+        <v>5.56</v>
+      </c>
+      <c r="L84">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M84">
+        <v>5.815735200000001</v>
+      </c>
+      <c r="N84">
+        <v>-5.2557352</v>
+      </c>
+      <c r="O84">
+        <v>-1.05114704</v>
+      </c>
+      <c r="P84">
+        <v>-4.20458816</v>
+      </c>
+      <c r="Q84">
+        <v>1.355411839999999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3412456814383346</v>
+      </c>
+      <c r="T84">
+        <v>4.579763791301568</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01925809827104922</v>
+      </c>
+      <c r="W84">
+        <v>0.2342011661328735</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.09629049135524614</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2554691788878564</v>
+      </c>
+      <c r="C85">
+        <v>-4.69922550892186</v>
+      </c>
+      <c r="D85">
+        <v>12.37177449107814</v>
+      </c>
+      <c r="E85">
+        <v>6.751000000000001</v>
+      </c>
+      <c r="F85">
+        <v>24.651</v>
+      </c>
+      <c r="G85">
+        <v>7.58</v>
+      </c>
+      <c r="H85">
+        <v>11.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.12</v>
+      </c>
+      <c r="K85">
+        <v>5.56</v>
+      </c>
+      <c r="L85">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M85">
+        <v>5.8866588</v>
+      </c>
+      <c r="N85">
+        <v>-5.3266588</v>
+      </c>
+      <c r="O85">
+        <v>-1.06533176</v>
+      </c>
+      <c r="P85">
+        <v>-4.26132704</v>
+      </c>
+      <c r="Q85">
+        <v>1.298672959999999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3590366038758837</v>
+      </c>
+      <c r="T85">
+        <v>4.849161661378131</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01902607299067513</v>
+      </c>
+      <c r="W85">
+        <v>0.2342565737698268</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.09513036495337568</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2574691788878564</v>
+      </c>
+      <c r="C86">
+        <v>-5.062954768205866</v>
+      </c>
+      <c r="D86">
+        <v>12.30504523179413</v>
+      </c>
+      <c r="E86">
+        <v>7.047999999999998</v>
+      </c>
+      <c r="F86">
+        <v>24.948</v>
+      </c>
+      <c r="G86">
+        <v>7.58</v>
+      </c>
+      <c r="H86">
+        <v>11.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.12</v>
+      </c>
+      <c r="K86">
+        <v>5.56</v>
+      </c>
+      <c r="L86">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M86">
+        <v>5.9575824</v>
+      </c>
+      <c r="N86">
+        <v>-5.397582399999999</v>
+      </c>
+      <c r="O86">
+        <v>-1.07951648</v>
+      </c>
+      <c r="P86">
+        <v>-4.31806592</v>
+      </c>
+      <c r="Q86">
+        <v>1.24193408</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3790513916181262</v>
+      </c>
+      <c r="T86">
+        <v>5.152234265214261</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01879957212173852</v>
+      </c>
+      <c r="W86">
+        <v>0.2343106621773288</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.09399786060869264</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2594691788878564</v>
+      </c>
+      <c r="C87">
+        <v>-5.425968058088095</v>
+      </c>
+      <c r="D87">
+        <v>12.2390319419119</v>
+      </c>
+      <c r="E87">
+        <v>7.344999999999999</v>
+      </c>
+      <c r="F87">
+        <v>25.245</v>
+      </c>
+      <c r="G87">
+        <v>7.58</v>
+      </c>
+      <c r="H87">
+        <v>11.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.12</v>
+      </c>
+      <c r="K87">
+        <v>5.56</v>
+      </c>
+      <c r="L87">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M87">
+        <v>6.028506</v>
+      </c>
+      <c r="N87">
+        <v>-5.468506</v>
+      </c>
+      <c r="O87">
+        <v>-1.0937012</v>
+      </c>
+      <c r="P87">
+        <v>-4.3748048</v>
+      </c>
+      <c r="Q87">
+        <v>1.1851952</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4017348177260013</v>
+      </c>
+      <c r="T87">
+        <v>5.495716549561879</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01857840068501218</v>
+      </c>
+      <c r="W87">
+        <v>0.2343634779164191</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09289200342506099</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2614691788878565</v>
+      </c>
+      <c r="C88">
+        <v>-5.788276840036193</v>
+      </c>
+      <c r="D88">
+        <v>12.1737231599638</v>
+      </c>
+      <c r="E88">
+        <v>7.641999999999999</v>
+      </c>
+      <c r="F88">
+        <v>25.542</v>
+      </c>
+      <c r="G88">
+        <v>7.58</v>
+      </c>
+      <c r="H88">
+        <v>11.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.12</v>
+      </c>
+      <c r="K88">
+        <v>5.56</v>
+      </c>
+      <c r="L88">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M88">
+        <v>6.0994296</v>
+      </c>
+      <c r="N88">
+        <v>-5.539429599999999</v>
+      </c>
+      <c r="O88">
+        <v>-1.10788592</v>
+      </c>
+      <c r="P88">
+        <v>-4.43154368</v>
+      </c>
+      <c r="Q88">
+        <v>1.12845632</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4276587332778586</v>
+      </c>
+      <c r="T88">
+        <v>5.888267731673443</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01836237277007019</v>
+      </c>
+      <c r="W88">
+        <v>0.2344150653825073</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09181186385035089</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2634691788878564</v>
+      </c>
+      <c r="C89">
+        <v>-6.149892332177828</v>
+      </c>
+      <c r="D89">
+        <v>12.10910766782217</v>
+      </c>
+      <c r="E89">
+        <v>7.939</v>
+      </c>
+      <c r="F89">
+        <v>25.839</v>
+      </c>
+      <c r="G89">
+        <v>7.58</v>
+      </c>
+      <c r="H89">
+        <v>11.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.12</v>
+      </c>
+      <c r="K89">
+        <v>5.56</v>
+      </c>
+      <c r="L89">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M89">
+        <v>6.1703532</v>
+      </c>
+      <c r="N89">
+        <v>-5.6103532</v>
+      </c>
+      <c r="O89">
+        <v>-1.12207064</v>
+      </c>
+      <c r="P89">
+        <v>-4.48828256</v>
+      </c>
+      <c r="Q89">
+        <v>1.07171744</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4575709435300016</v>
+      </c>
+      <c r="T89">
+        <v>6.34121140334063</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01815131101409237</v>
+      </c>
+      <c r="W89">
+        <v>0.2344654669298347</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09075655507046188</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2654691788878564</v>
+      </c>
+      <c r="C90">
+        <v>-6.51082551572458</v>
+      </c>
+      <c r="D90">
+        <v>12.04517448427542</v>
+      </c>
+      <c r="E90">
+        <v>8.236000000000001</v>
+      </c>
+      <c r="F90">
+        <v>26.136</v>
+      </c>
+      <c r="G90">
+        <v>7.58</v>
+      </c>
+      <c r="H90">
+        <v>11.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.12</v>
+      </c>
+      <c r="K90">
+        <v>5.56</v>
+      </c>
+      <c r="L90">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M90">
+        <v>6.241276800000001</v>
+      </c>
+      <c r="N90">
+        <v>-5.6812768</v>
+      </c>
+      <c r="O90">
+        <v>-1.13625536</v>
+      </c>
+      <c r="P90">
+        <v>-4.54502144</v>
+      </c>
+      <c r="Q90">
+        <v>1.014978559999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4924685221575018</v>
+      </c>
+      <c r="T90">
+        <v>6.86964568695235</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01794504611620495</v>
+      </c>
+      <c r="W90">
+        <v>0.2345147229874503</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.08972523058102477</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2674691788878564</v>
+      </c>
+      <c r="C91">
+        <v>-6.871087141193392</v>
+      </c>
+      <c r="D91">
+        <v>11.98191285880661</v>
+      </c>
+      <c r="E91">
+        <v>8.533000000000001</v>
+      </c>
+      <c r="F91">
+        <v>26.433</v>
+      </c>
+      <c r="G91">
+        <v>7.58</v>
+      </c>
+      <c r="H91">
+        <v>11.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.12</v>
+      </c>
+      <c r="K91">
+        <v>5.56</v>
+      </c>
+      <c r="L91">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M91">
+        <v>6.3122004</v>
+      </c>
+      <c r="N91">
+        <v>-5.7522004</v>
+      </c>
+      <c r="O91">
+        <v>-1.15044008</v>
+      </c>
+      <c r="P91">
+        <v>-4.60176032</v>
+      </c>
+      <c r="Q91">
+        <v>0.9582396799999993</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5337111150809111</v>
+      </c>
+      <c r="T91">
+        <v>7.494158931220746</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0177434163845622</v>
+      </c>
+      <c r="W91">
+        <v>0.2345628721673665</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.08871708192281103</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2694691788878564</v>
+      </c>
+      <c r="C92">
+        <v>-7.230687734432987</v>
+      </c>
+      <c r="D92">
+        <v>11.91931226556701</v>
+      </c>
+      <c r="E92">
+        <v>8.830000000000002</v>
+      </c>
+      <c r="F92">
+        <v>26.73</v>
+      </c>
+      <c r="G92">
+        <v>7.58</v>
+      </c>
+      <c r="H92">
+        <v>11.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.12</v>
+      </c>
+      <c r="K92">
+        <v>5.56</v>
+      </c>
+      <c r="L92">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M92">
+        <v>6.383124</v>
+      </c>
+      <c r="N92">
+        <v>-5.823124</v>
+      </c>
+      <c r="O92">
+        <v>-1.1646248</v>
+      </c>
+      <c r="P92">
+        <v>-4.658499200000001</v>
+      </c>
+      <c r="Q92">
+        <v>0.9015007999999991</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5832022265890022</v>
+      </c>
+      <c r="T92">
+        <v>8.24357482434282</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01754626731362262</v>
+      </c>
+      <c r="W92">
+        <v>0.2346099513655069</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08773133656811316</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2714691788878564</v>
+      </c>
+      <c r="C93">
+        <v>-7.589637602462382</v>
+      </c>
+      <c r="D93">
+        <v>11.85736239753762</v>
+      </c>
+      <c r="E93">
+        <v>9.127000000000002</v>
+      </c>
+      <c r="F93">
+        <v>27.027</v>
+      </c>
+      <c r="G93">
+        <v>7.58</v>
+      </c>
+      <c r="H93">
+        <v>11.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.12</v>
+      </c>
+      <c r="K93">
+        <v>5.56</v>
+      </c>
+      <c r="L93">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M93">
+        <v>6.454047600000001</v>
+      </c>
+      <c r="N93">
+        <v>-5.8940476</v>
+      </c>
+      <c r="O93">
+        <v>-1.17880952</v>
+      </c>
+      <c r="P93">
+        <v>-4.715238080000001</v>
+      </c>
+      <c r="Q93">
+        <v>0.8447619199999989</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6436913628766692</v>
+      </c>
+      <c r="T93">
+        <v>9.159527582603136</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01735345118929709</v>
+      </c>
+      <c r="W93">
+        <v>0.2346559958559959</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.08676725594648549</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2734691788878564</v>
+      </c>
+      <c r="C94">
+        <v>-7.947946839128225</v>
+      </c>
+      <c r="D94">
+        <v>11.79605316087178</v>
+      </c>
+      <c r="E94">
+        <v>9.424000000000003</v>
+      </c>
+      <c r="F94">
+        <v>27.324</v>
+      </c>
+      <c r="G94">
+        <v>7.58</v>
+      </c>
+      <c r="H94">
+        <v>11.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.12</v>
+      </c>
+      <c r="K94">
+        <v>5.56</v>
+      </c>
+      <c r="L94">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M94">
+        <v>6.5249712</v>
+      </c>
+      <c r="N94">
+        <v>-5.9649712</v>
+      </c>
+      <c r="O94">
+        <v>-1.19299424</v>
+      </c>
+      <c r="P94">
+        <v>-4.77197696</v>
+      </c>
+      <c r="Q94">
+        <v>0.7880230399999997</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7193027832362529</v>
+      </c>
+      <c r="T94">
+        <v>10.30446853042853</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01716482671984822</v>
+      </c>
+      <c r="W94">
+        <v>0.2347010393793003</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08582413359924113</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2754691788878564</v>
+      </c>
+      <c r="C95">
+        <v>-8.305625330587567</v>
+      </c>
+      <c r="D95">
+        <v>11.73537466941244</v>
+      </c>
+      <c r="E95">
+        <v>9.721000000000004</v>
+      </c>
+      <c r="F95">
+        <v>27.621</v>
+      </c>
+      <c r="G95">
+        <v>7.58</v>
+      </c>
+      <c r="H95">
+        <v>11.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.12</v>
+      </c>
+      <c r="K95">
+        <v>5.56</v>
+      </c>
+      <c r="L95">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M95">
+        <v>6.595894800000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.0358948</v>
+      </c>
+      <c r="O95">
+        <v>-1.20717896</v>
+      </c>
+      <c r="P95">
+        <v>-4.828715840000001</v>
+      </c>
+      <c r="Q95">
+        <v>0.7312841599999986</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8165174665557178</v>
+      </c>
+      <c r="T95">
+        <v>11.77653546334689</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01698025869060254</v>
+      </c>
+      <c r="W95">
+        <v>0.2347451142246841</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08490129345301267</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2774691788878564</v>
+      </c>
+      <c r="C96">
+        <v>-8.662682760622271</v>
+      </c>
+      <c r="D96">
+        <v>11.67531723937773</v>
+      </c>
+      <c r="E96">
+        <v>10.018</v>
+      </c>
+      <c r="F96">
+        <v>27.918</v>
+      </c>
+      <c r="G96">
+        <v>7.58</v>
+      </c>
+      <c r="H96">
+        <v>11.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.12</v>
+      </c>
+      <c r="K96">
+        <v>5.56</v>
+      </c>
+      <c r="L96">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M96">
+        <v>6.666818400000001</v>
+      </c>
+      <c r="N96">
+        <v>-6.106818400000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.22136368</v>
+      </c>
+      <c r="P96">
+        <v>-4.885454720000001</v>
+      </c>
+      <c r="Q96">
+        <v>0.6745452799999985</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9461370443150043</v>
+      </c>
+      <c r="T96">
+        <v>13.73929137390471</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01679961764070251</v>
+      </c>
+      <c r="W96">
+        <v>0.2347882513074002</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.08399808820351251</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2794691788878565</v>
+      </c>
+      <c r="C97">
+        <v>-9.01912861579105</v>
+      </c>
+      <c r="D97">
+        <v>11.61587138420895</v>
+      </c>
+      <c r="E97">
+        <v>10.315</v>
+      </c>
+      <c r="F97">
+        <v>28.215</v>
+      </c>
+      <c r="G97">
+        <v>7.58</v>
+      </c>
+      <c r="H97">
+        <v>11.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.12</v>
+      </c>
+      <c r="K97">
+        <v>5.56</v>
+      </c>
+      <c r="L97">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M97">
+        <v>6.737742</v>
+      </c>
+      <c r="N97">
+        <v>-6.177741999999999</v>
+      </c>
+      <c r="O97">
+        <v>-1.2355484</v>
+      </c>
+      <c r="P97">
+        <v>-4.9421936</v>
+      </c>
+      <c r="Q97">
+        <v>0.6178064000000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.127604453178006</v>
+      </c>
+      <c r="T97">
+        <v>16.48714964868566</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01662277956027406</v>
+      </c>
+      <c r="W97">
+        <v>0.2348304802410066</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08311389780137035</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2814691788878564</v>
+      </c>
+      <c r="C98">
+        <v>-9.374972190424923</v>
+      </c>
+      <c r="D98">
+        <v>11.55702780957507</v>
+      </c>
+      <c r="E98">
+        <v>10.612</v>
+      </c>
+      <c r="F98">
+        <v>28.512</v>
+      </c>
+      <c r="G98">
+        <v>7.58</v>
+      </c>
+      <c r="H98">
+        <v>11.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.12</v>
+      </c>
+      <c r="K98">
+        <v>5.56</v>
+      </c>
+      <c r="L98">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M98">
+        <v>6.808665599999999</v>
+      </c>
+      <c r="N98">
+        <v>-6.248665599999999</v>
+      </c>
+      <c r="O98">
+        <v>-1.249733119999999</v>
+      </c>
+      <c r="P98">
+        <v>-4.99893248</v>
+      </c>
+      <c r="Q98">
+        <v>0.5610675199999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.399805566472504</v>
+      </c>
+      <c r="T98">
+        <v>20.60893706085703</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01644962560652121</v>
+      </c>
+      <c r="W98">
+        <v>0.2348718294051627</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.08224812803260606</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2834691788878564</v>
+      </c>
+      <c r="C99">
+        <v>-9.730222591471627</v>
+      </c>
+      <c r="D99">
+        <v>11.49877740852837</v>
+      </c>
+      <c r="E99">
+        <v>10.909</v>
+      </c>
+      <c r="F99">
+        <v>28.809</v>
+      </c>
+      <c r="G99">
+        <v>7.58</v>
+      </c>
+      <c r="H99">
+        <v>11.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.12</v>
+      </c>
+      <c r="K99">
+        <v>5.56</v>
+      </c>
+      <c r="L99">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M99">
+        <v>6.8795892</v>
+      </c>
+      <c r="N99">
+        <v>-6.319589199999999</v>
+      </c>
+      <c r="O99">
+        <v>-1.26391784</v>
+      </c>
+      <c r="P99">
+        <v>-5.05567136</v>
+      </c>
+      <c r="Q99">
+        <v>0.5043286399999998</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.853474088630006</v>
+      </c>
+      <c r="T99">
+        <v>27.47858274780938</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01628004183738182</v>
+      </c>
+      <c r="W99">
+        <v>0.2349123260092332</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08140020918690904</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2854691788878564</v>
+      </c>
+      <c r="C100">
+        <v>-10.0848887431942</v>
+      </c>
+      <c r="D100">
+        <v>11.4411112568058</v>
+      </c>
+      <c r="E100">
+        <v>11.206</v>
+      </c>
+      <c r="F100">
+        <v>29.106</v>
+      </c>
+      <c r="G100">
+        <v>7.58</v>
+      </c>
+      <c r="H100">
+        <v>11.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.12</v>
+      </c>
+      <c r="K100">
+        <v>5.56</v>
+      </c>
+      <c r="L100">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M100">
+        <v>6.9505128</v>
+      </c>
+      <c r="N100">
+        <v>-6.3905128</v>
+      </c>
+      <c r="O100">
+        <v>-1.27810256</v>
+      </c>
+      <c r="P100">
+        <v>-5.11241024</v>
+      </c>
+      <c r="Q100">
+        <v>0.4475897599999996</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.760811132945008</v>
+      </c>
+      <c r="T100">
+        <v>41.21787412171406</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01611391896149016</v>
+      </c>
+      <c r="W100">
+        <v>0.2349519961519962</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08056959480745085</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2874691788878564</v>
+      </c>
+      <c r="C101">
+        <v>-10.43897939172893</v>
+      </c>
+      <c r="D101">
+        <v>11.38402060827107</v>
+      </c>
+      <c r="E101">
+        <v>11.503</v>
+      </c>
+      <c r="F101">
+        <v>29.403</v>
+      </c>
+      <c r="G101">
+        <v>7.58</v>
+      </c>
+      <c r="H101">
+        <v>11.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.12</v>
+      </c>
+      <c r="K101">
+        <v>5.56</v>
+      </c>
+      <c r="L101">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="M101">
+        <v>7.0214364</v>
+      </c>
+      <c r="N101">
+        <v>-6.461436399999999</v>
+      </c>
+      <c r="O101">
+        <v>-1.29228728</v>
+      </c>
+      <c r="P101">
+        <v>-5.16914912</v>
+      </c>
+      <c r="Q101">
+        <v>0.3908508799999995</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.482822265890016</v>
+      </c>
+      <c r="T101">
+        <v>82.43574824342812</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01595115210329329</v>
+      </c>
+      <c r="W101">
+        <v>0.2349908648777336</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.07975576051646649</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
